--- a/output/reports/サンプル/サンプル2.xlsx
+++ b/output/reports/サンプル/サンプル2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="96" yWindow="312" windowWidth="11868" windowHeight="12816" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" state="visible" r:id="rId1"/>
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Yu Gothic"/>
       <family val="2"/>
@@ -63,14 +63,6 @@
       <family val="2"/>
       <color theme="1"/>
       <sz val="16"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Yu Gothic"/>
-      <charset val="128"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -265,31 +257,31 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -298,106 +290,108 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -407,16 +401,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -983,90 +967,90 @@
   <dimension ref="C12:AB44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="1" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="11" ht="15" customHeight="1" thickBot="1"/>
     <row r="12" ht="15" customHeight="1">
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="40" t="inlineStr">
         <is>
           <t>保育園欠席データ分析報告書</t>
         </is>
       </c>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="35" t="n"/>
-      <c r="G12" s="35" t="n"/>
-      <c r="H12" s="35" t="n"/>
-      <c r="I12" s="35" t="n"/>
-      <c r="J12" s="35" t="n"/>
-      <c r="K12" s="35" t="n"/>
-      <c r="L12" s="35" t="n"/>
-      <c r="M12" s="35" t="n"/>
-      <c r="N12" s="35" t="n"/>
-      <c r="O12" s="35" t="n"/>
-      <c r="P12" s="35" t="n"/>
-      <c r="Q12" s="35" t="n"/>
-      <c r="R12" s="35" t="n"/>
-      <c r="S12" s="35" t="n"/>
-      <c r="T12" s="35" t="n"/>
-      <c r="U12" s="35" t="n"/>
-      <c r="V12" s="35" t="n"/>
-      <c r="W12" s="35" t="n"/>
-      <c r="X12" s="35" t="n"/>
-      <c r="Y12" s="35" t="n"/>
-      <c r="Z12" s="35" t="n"/>
-      <c r="AA12" s="35" t="n"/>
-      <c r="AB12" s="36" t="n"/>
+      <c r="D12" s="41" t="n"/>
+      <c r="E12" s="41" t="n"/>
+      <c r="F12" s="41" t="n"/>
+      <c r="G12" s="41" t="n"/>
+      <c r="H12" s="41" t="n"/>
+      <c r="I12" s="41" t="n"/>
+      <c r="J12" s="41" t="n"/>
+      <c r="K12" s="41" t="n"/>
+      <c r="L12" s="41" t="n"/>
+      <c r="M12" s="41" t="n"/>
+      <c r="N12" s="41" t="n"/>
+      <c r="O12" s="41" t="n"/>
+      <c r="P12" s="41" t="n"/>
+      <c r="Q12" s="41" t="n"/>
+      <c r="R12" s="41" t="n"/>
+      <c r="S12" s="41" t="n"/>
+      <c r="T12" s="41" t="n"/>
+      <c r="U12" s="41" t="n"/>
+      <c r="V12" s="41" t="n"/>
+      <c r="W12" s="41" t="n"/>
+      <c r="X12" s="41" t="n"/>
+      <c r="Y12" s="41" t="n"/>
+      <c r="Z12" s="41" t="n"/>
+      <c r="AA12" s="41" t="n"/>
+      <c r="AB12" s="42" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="C13" s="37" t="n"/>
-      <c r="AB13" s="38" t="n"/>
+      <c r="C13" s="43" t="n"/>
+      <c r="AB13" s="44" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="C14" s="37" t="n"/>
-      <c r="AB14" s="38" t="n"/>
+      <c r="C14" s="43" t="n"/>
+      <c r="AB14" s="44" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="C15" s="37" t="n"/>
-      <c r="AB15" s="38" t="n"/>
+      <c r="C15" s="43" t="n"/>
+      <c r="AB15" s="44" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="C16" s="37" t="n"/>
-      <c r="AB16" s="38" t="n"/>
+      <c r="C16" s="43" t="n"/>
+      <c r="AB16" s="44" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" thickBot="1">
-      <c r="C17" s="39" t="n"/>
-      <c r="D17" s="40" t="n"/>
-      <c r="E17" s="40" t="n"/>
-      <c r="F17" s="40" t="n"/>
-      <c r="G17" s="40" t="n"/>
-      <c r="H17" s="40" t="n"/>
-      <c r="I17" s="40" t="n"/>
-      <c r="J17" s="40" t="n"/>
-      <c r="K17" s="40" t="n"/>
-      <c r="L17" s="40" t="n"/>
-      <c r="M17" s="40" t="n"/>
-      <c r="N17" s="40" t="n"/>
-      <c r="O17" s="40" t="n"/>
-      <c r="P17" s="40" t="n"/>
-      <c r="Q17" s="40" t="n"/>
-      <c r="R17" s="40" t="n"/>
-      <c r="S17" s="40" t="n"/>
-      <c r="T17" s="40" t="n"/>
-      <c r="U17" s="40" t="n"/>
-      <c r="V17" s="40" t="n"/>
-      <c r="W17" s="40" t="n"/>
-      <c r="X17" s="40" t="n"/>
-      <c r="Y17" s="40" t="n"/>
-      <c r="Z17" s="40" t="n"/>
-      <c r="AA17" s="40" t="n"/>
-      <c r="AB17" s="41" t="n"/>
+      <c r="C17" s="45" t="n"/>
+      <c r="D17" s="46" t="n"/>
+      <c r="E17" s="46" t="n"/>
+      <c r="F17" s="46" t="n"/>
+      <c r="G17" s="46" t="n"/>
+      <c r="H17" s="46" t="n"/>
+      <c r="I17" s="46" t="n"/>
+      <c r="J17" s="46" t="n"/>
+      <c r="K17" s="46" t="n"/>
+      <c r="L17" s="46" t="n"/>
+      <c r="M17" s="46" t="n"/>
+      <c r="N17" s="46" t="n"/>
+      <c r="O17" s="46" t="n"/>
+      <c r="P17" s="46" t="n"/>
+      <c r="Q17" s="46" t="n"/>
+      <c r="R17" s="46" t="n"/>
+      <c r="S17" s="46" t="n"/>
+      <c r="T17" s="46" t="n"/>
+      <c r="U17" s="46" t="n"/>
+      <c r="V17" s="46" t="n"/>
+      <c r="W17" s="46" t="n"/>
+      <c r="X17" s="46" t="n"/>
+      <c r="Y17" s="46" t="n"/>
+      <c r="Z17" s="46" t="n"/>
+      <c r="AA17" s="46" t="n"/>
+      <c r="AB17" s="47" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="J44" s="23" t="inlineStr">
-        <is>
-          <t>2026/07/01</t>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>2026/07/02</t>
         </is>
       </c>
     </row>
@@ -1089,11 +1073,11 @@
   <dimension ref="B2:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="1" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>3.総合所見</t>
         </is>
@@ -1101,95 +1085,95 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="4" ht="15" customHeight="1">
-      <c r="B4" s="42" t="inlineStr">
-        <is>
-          <t>過去データおよびAI（LightGBM回帰モデル）予測を総合すると、将来における対象児童の平均欠席日数は月あたり約2.6日と推定された。成長や通園期間に伴い全体的には改善傾向を辿る見込みであるが、季節要因による突発的な変動リスクに対しては、今後も継続的な警戒必要である。</t>
-        </is>
-      </c>
-      <c r="C4" s="43" t="n"/>
-      <c r="D4" s="43" t="n"/>
-      <c r="E4" s="43" t="n"/>
-      <c r="F4" s="43" t="n"/>
-      <c r="G4" s="43" t="n"/>
-      <c r="H4" s="43" t="n"/>
-      <c r="I4" s="43" t="n"/>
-      <c r="J4" s="43" t="n"/>
-      <c r="K4" s="43" t="n"/>
-      <c r="L4" s="43" t="n"/>
-      <c r="M4" s="43" t="n"/>
-      <c r="N4" s="43" t="n"/>
-      <c r="O4" s="43" t="n"/>
-      <c r="P4" s="43" t="n"/>
-      <c r="Q4" s="43" t="n"/>
-      <c r="R4" s="43" t="n"/>
-      <c r="S4" s="43" t="n"/>
-      <c r="T4" s="43" t="n"/>
-      <c r="U4" s="43" t="n"/>
-      <c r="V4" s="43" t="n"/>
-      <c r="W4" s="43" t="n"/>
-      <c r="X4" s="43" t="n"/>
-      <c r="Y4" s="43" t="n"/>
-      <c r="Z4" s="43" t="n"/>
-      <c r="AA4" s="43" t="n"/>
-      <c r="AB4" s="43" t="n"/>
-      <c r="AC4" s="44" t="n"/>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>AI（LightGBM回帰モデル）による未来予測では、対象児童2名の平均予測欠席日数は月あたり約2.6日と推定された。予測期間内に安定化が見込まれる児童はいなかった。継続的な健康観察と家庭との連携を強化し、個々の状況に応じた支援を継続することが望まれる。</t>
+        </is>
+      </c>
+      <c r="C4" s="34" t="n"/>
+      <c r="D4" s="34" t="n"/>
+      <c r="E4" s="34" t="n"/>
+      <c r="F4" s="34" t="n"/>
+      <c r="G4" s="34" t="n"/>
+      <c r="H4" s="34" t="n"/>
+      <c r="I4" s="34" t="n"/>
+      <c r="J4" s="34" t="n"/>
+      <c r="K4" s="34" t="n"/>
+      <c r="L4" s="34" t="n"/>
+      <c r="M4" s="34" t="n"/>
+      <c r="N4" s="34" t="n"/>
+      <c r="O4" s="34" t="n"/>
+      <c r="P4" s="34" t="n"/>
+      <c r="Q4" s="34" t="n"/>
+      <c r="R4" s="34" t="n"/>
+      <c r="S4" s="34" t="n"/>
+      <c r="T4" s="34" t="n"/>
+      <c r="U4" s="34" t="n"/>
+      <c r="V4" s="34" t="n"/>
+      <c r="W4" s="34" t="n"/>
+      <c r="X4" s="34" t="n"/>
+      <c r="Y4" s="34" t="n"/>
+      <c r="Z4" s="34" t="n"/>
+      <c r="AA4" s="34" t="n"/>
+      <c r="AB4" s="34" t="n"/>
+      <c r="AC4" s="35" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="45" t="n"/>
-      <c r="AC5" s="46" t="n"/>
+      <c r="B5" s="36" t="n"/>
+      <c r="AC5" s="37" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="45" t="n"/>
-      <c r="AC6" s="46" t="n"/>
+      <c r="B6" s="36" t="n"/>
+      <c r="AC6" s="37" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="45" t="n"/>
-      <c r="AC7" s="46" t="n"/>
+      <c r="B7" s="36" t="n"/>
+      <c r="AC7" s="37" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="45" t="n"/>
-      <c r="AC8" s="46" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="AC8" s="37" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="B9" s="45" t="n"/>
-      <c r="AC9" s="46" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="AC9" s="37" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="45" t="n"/>
-      <c r="AC10" s="46" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="AC10" s="37" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="B11" s="47" t="n"/>
-      <c r="C11" s="48" t="n"/>
-      <c r="D11" s="48" t="n"/>
-      <c r="E11" s="48" t="n"/>
-      <c r="F11" s="48" t="n"/>
-      <c r="G11" s="48" t="n"/>
-      <c r="H11" s="48" t="n"/>
-      <c r="I11" s="48" t="n"/>
-      <c r="J11" s="48" t="n"/>
-      <c r="K11" s="48" t="n"/>
-      <c r="L11" s="48" t="n"/>
-      <c r="M11" s="48" t="n"/>
-      <c r="N11" s="48" t="n"/>
-      <c r="O11" s="48" t="n"/>
-      <c r="P11" s="48" t="n"/>
-      <c r="Q11" s="48" t="n"/>
-      <c r="R11" s="48" t="n"/>
-      <c r="S11" s="48" t="n"/>
-      <c r="T11" s="48" t="n"/>
-      <c r="U11" s="48" t="n"/>
-      <c r="V11" s="48" t="n"/>
-      <c r="W11" s="48" t="n"/>
-      <c r="X11" s="48" t="n"/>
-      <c r="Y11" s="48" t="n"/>
-      <c r="Z11" s="48" t="n"/>
-      <c r="AA11" s="48" t="n"/>
-      <c r="AB11" s="48" t="n"/>
-      <c r="AC11" s="49" t="n"/>
+      <c r="B11" s="38" t="n"/>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="32" t="n"/>
+      <c r="E11" s="32" t="n"/>
+      <c r="F11" s="32" t="n"/>
+      <c r="G11" s="32" t="n"/>
+      <c r="H11" s="32" t="n"/>
+      <c r="I11" s="32" t="n"/>
+      <c r="J11" s="32" t="n"/>
+      <c r="K11" s="32" t="n"/>
+      <c r="L11" s="32" t="n"/>
+      <c r="M11" s="32" t="n"/>
+      <c r="N11" s="32" t="n"/>
+      <c r="O11" s="32" t="n"/>
+      <c r="P11" s="32" t="n"/>
+      <c r="Q11" s="32" t="n"/>
+      <c r="R11" s="32" t="n"/>
+      <c r="S11" s="32" t="n"/>
+      <c r="T11" s="32" t="n"/>
+      <c r="U11" s="32" t="n"/>
+      <c r="V11" s="32" t="n"/>
+      <c r="W11" s="32" t="n"/>
+      <c r="X11" s="32" t="n"/>
+      <c r="Y11" s="32" t="n"/>
+      <c r="Z11" s="32" t="n"/>
+      <c r="AA11" s="32" t="n"/>
+      <c r="AB11" s="32" t="n"/>
+      <c r="AC11" s="39" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>4.結論</t>
         </is>
@@ -1197,92 +1181,92 @@
     </row>
     <row r="15" ht="15" customHeight="1"/>
     <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="42" t="inlineStr">
-        <is>
-          <t>予測期間内に明確な安定化基準を満たす時期は現時点で確認されなかった。引き続き個別的な健康管理と予防的アプローチを強化しながら、経過観察を行うことが推奨される。</t>
-        </is>
-      </c>
-      <c r="C16" s="43" t="n"/>
-      <c r="D16" s="43" t="n"/>
-      <c r="E16" s="43" t="n"/>
-      <c r="F16" s="43" t="n"/>
-      <c r="G16" s="43" t="n"/>
-      <c r="H16" s="43" t="n"/>
-      <c r="I16" s="43" t="n"/>
-      <c r="J16" s="43" t="n"/>
-      <c r="K16" s="43" t="n"/>
-      <c r="L16" s="43" t="n"/>
-      <c r="M16" s="43" t="n"/>
-      <c r="N16" s="43" t="n"/>
-      <c r="O16" s="43" t="n"/>
-      <c r="P16" s="43" t="n"/>
-      <c r="Q16" s="43" t="n"/>
-      <c r="R16" s="43" t="n"/>
-      <c r="S16" s="43" t="n"/>
-      <c r="T16" s="43" t="n"/>
-      <c r="U16" s="43" t="n"/>
-      <c r="V16" s="43" t="n"/>
-      <c r="W16" s="43" t="n"/>
-      <c r="X16" s="43" t="n"/>
-      <c r="Y16" s="43" t="n"/>
-      <c r="Z16" s="43" t="n"/>
-      <c r="AA16" s="43" t="n"/>
-      <c r="AB16" s="43" t="n"/>
-      <c r="AC16" s="44" t="n"/>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>AI（LightGBM回帰モデル）による予測では、予測期間内に安定化が見込まれる児童は確認されなかった。今後も継続的な健康観察や家庭との連携を行いながら、児童一人ひとりの状況に応じた支援を継続することが重要である。本システムは欠席傾向を可視化し、継続的な健康管理を支援するための参考資料として活用できる。</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="34" t="n"/>
+      <c r="E16" s="34" t="n"/>
+      <c r="F16" s="34" t="n"/>
+      <c r="G16" s="34" t="n"/>
+      <c r="H16" s="34" t="n"/>
+      <c r="I16" s="34" t="n"/>
+      <c r="J16" s="34" t="n"/>
+      <c r="K16" s="34" t="n"/>
+      <c r="L16" s="34" t="n"/>
+      <c r="M16" s="34" t="n"/>
+      <c r="N16" s="34" t="n"/>
+      <c r="O16" s="34" t="n"/>
+      <c r="P16" s="34" t="n"/>
+      <c r="Q16" s="34" t="n"/>
+      <c r="R16" s="34" t="n"/>
+      <c r="S16" s="34" t="n"/>
+      <c r="T16" s="34" t="n"/>
+      <c r="U16" s="34" t="n"/>
+      <c r="V16" s="34" t="n"/>
+      <c r="W16" s="34" t="n"/>
+      <c r="X16" s="34" t="n"/>
+      <c r="Y16" s="34" t="n"/>
+      <c r="Z16" s="34" t="n"/>
+      <c r="AA16" s="34" t="n"/>
+      <c r="AB16" s="34" t="n"/>
+      <c r="AC16" s="35" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="45" t="n"/>
-      <c r="AC17" s="46" t="n"/>
+      <c r="B17" s="36" t="n"/>
+      <c r="AC17" s="37" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="45" t="n"/>
-      <c r="AC18" s="46" t="n"/>
+      <c r="B18" s="36" t="n"/>
+      <c r="AC18" s="37" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="B19" s="45" t="n"/>
-      <c r="AC19" s="46" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="AC19" s="37" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="B20" s="45" t="n"/>
-      <c r="AC20" s="46" t="n"/>
+      <c r="B20" s="36" t="n"/>
+      <c r="AC20" s="37" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="B21" s="45" t="n"/>
-      <c r="AC21" s="46" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="AC21" s="37" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="45" t="n"/>
-      <c r="AC22" s="46" t="n"/>
+      <c r="B22" s="36" t="n"/>
+      <c r="AC22" s="37" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="47" t="n"/>
-      <c r="C23" s="48" t="n"/>
-      <c r="D23" s="48" t="n"/>
-      <c r="E23" s="48" t="n"/>
-      <c r="F23" s="48" t="n"/>
-      <c r="G23" s="48" t="n"/>
-      <c r="H23" s="48" t="n"/>
-      <c r="I23" s="48" t="n"/>
-      <c r="J23" s="48" t="n"/>
-      <c r="K23" s="48" t="n"/>
-      <c r="L23" s="48" t="n"/>
-      <c r="M23" s="48" t="n"/>
-      <c r="N23" s="48" t="n"/>
-      <c r="O23" s="48" t="n"/>
-      <c r="P23" s="48" t="n"/>
-      <c r="Q23" s="48" t="n"/>
-      <c r="R23" s="48" t="n"/>
-      <c r="S23" s="48" t="n"/>
-      <c r="T23" s="48" t="n"/>
-      <c r="U23" s="48" t="n"/>
-      <c r="V23" s="48" t="n"/>
-      <c r="W23" s="48" t="n"/>
-      <c r="X23" s="48" t="n"/>
-      <c r="Y23" s="48" t="n"/>
-      <c r="Z23" s="48" t="n"/>
-      <c r="AA23" s="48" t="n"/>
-      <c r="AB23" s="48" t="n"/>
-      <c r="AC23" s="49" t="n"/>
+      <c r="B23" s="38" t="n"/>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="32" t="n"/>
+      <c r="E23" s="32" t="n"/>
+      <c r="F23" s="32" t="n"/>
+      <c r="G23" s="32" t="n"/>
+      <c r="H23" s="32" t="n"/>
+      <c r="I23" s="32" t="n"/>
+      <c r="J23" s="32" t="n"/>
+      <c r="K23" s="32" t="n"/>
+      <c r="L23" s="32" t="n"/>
+      <c r="M23" s="32" t="n"/>
+      <c r="N23" s="32" t="n"/>
+      <c r="O23" s="32" t="n"/>
+      <c r="P23" s="32" t="n"/>
+      <c r="Q23" s="32" t="n"/>
+      <c r="R23" s="32" t="n"/>
+      <c r="S23" s="32" t="n"/>
+      <c r="T23" s="32" t="n"/>
+      <c r="U23" s="32" t="n"/>
+      <c r="V23" s="32" t="n"/>
+      <c r="W23" s="32" t="n"/>
+      <c r="X23" s="32" t="n"/>
+      <c r="Y23" s="32" t="n"/>
+      <c r="Z23" s="32" t="n"/>
+      <c r="AA23" s="32" t="n"/>
+      <c r="AB23" s="32" t="n"/>
+      <c r="AC23" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1305,7 +1289,7 @@
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="1" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1322,11 +1306,11 @@
   <dimension ref="B2:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="1" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>1-1.目的</t>
         </is>
@@ -1334,80 +1318,80 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>保育園における園児の欠席傾向を分析し、
 業務改善および将来リスク予測に活用する。</t>
         </is>
       </c>
-      <c r="C5" s="43" t="n"/>
-      <c r="D5" s="43" t="n"/>
-      <c r="E5" s="43" t="n"/>
-      <c r="F5" s="43" t="n"/>
-      <c r="G5" s="43" t="n"/>
-      <c r="H5" s="43" t="n"/>
-      <c r="I5" s="43" t="n"/>
-      <c r="J5" s="43" t="n"/>
-      <c r="K5" s="43" t="n"/>
-      <c r="L5" s="43" t="n"/>
-      <c r="M5" s="43" t="n"/>
-      <c r="N5" s="43" t="n"/>
-      <c r="O5" s="43" t="n"/>
-      <c r="P5" s="43" t="n"/>
-      <c r="Q5" s="43" t="n"/>
-      <c r="R5" s="43" t="n"/>
-      <c r="S5" s="43" t="n"/>
-      <c r="T5" s="43" t="n"/>
-      <c r="U5" s="43" t="n"/>
-      <c r="V5" s="43" t="n"/>
-      <c r="W5" s="43" t="n"/>
-      <c r="X5" s="43" t="n"/>
-      <c r="Y5" s="43" t="n"/>
-      <c r="Z5" s="43" t="n"/>
-      <c r="AA5" s="43" t="n"/>
-      <c r="AB5" s="43" t="n"/>
-      <c r="AC5" s="44" t="n"/>
+      <c r="C5" s="34" t="n"/>
+      <c r="D5" s="34" t="n"/>
+      <c r="E5" s="34" t="n"/>
+      <c r="F5" s="34" t="n"/>
+      <c r="G5" s="34" t="n"/>
+      <c r="H5" s="34" t="n"/>
+      <c r="I5" s="34" t="n"/>
+      <c r="J5" s="34" t="n"/>
+      <c r="K5" s="34" t="n"/>
+      <c r="L5" s="34" t="n"/>
+      <c r="M5" s="34" t="n"/>
+      <c r="N5" s="34" t="n"/>
+      <c r="O5" s="34" t="n"/>
+      <c r="P5" s="34" t="n"/>
+      <c r="Q5" s="34" t="n"/>
+      <c r="R5" s="34" t="n"/>
+      <c r="S5" s="34" t="n"/>
+      <c r="T5" s="34" t="n"/>
+      <c r="U5" s="34" t="n"/>
+      <c r="V5" s="34" t="n"/>
+      <c r="W5" s="34" t="n"/>
+      <c r="X5" s="34" t="n"/>
+      <c r="Y5" s="34" t="n"/>
+      <c r="Z5" s="34" t="n"/>
+      <c r="AA5" s="34" t="n"/>
+      <c r="AB5" s="34" t="n"/>
+      <c r="AC5" s="35" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="45" t="n"/>
-      <c r="AC6" s="46" t="n"/>
+      <c r="B6" s="36" t="n"/>
+      <c r="AC6" s="37" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="45" t="n"/>
-      <c r="AC7" s="46" t="n"/>
+      <c r="B7" s="36" t="n"/>
+      <c r="AC7" s="37" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="47" t="n"/>
-      <c r="C8" s="48" t="n"/>
-      <c r="D8" s="48" t="n"/>
-      <c r="E8" s="48" t="n"/>
-      <c r="F8" s="48" t="n"/>
-      <c r="G8" s="48" t="n"/>
-      <c r="H8" s="48" t="n"/>
-      <c r="I8" s="48" t="n"/>
-      <c r="J8" s="48" t="n"/>
-      <c r="K8" s="48" t="n"/>
-      <c r="L8" s="48" t="n"/>
-      <c r="M8" s="48" t="n"/>
-      <c r="N8" s="48" t="n"/>
-      <c r="O8" s="48" t="n"/>
-      <c r="P8" s="48" t="n"/>
-      <c r="Q8" s="48" t="n"/>
-      <c r="R8" s="48" t="n"/>
-      <c r="S8" s="48" t="n"/>
-      <c r="T8" s="48" t="n"/>
-      <c r="U8" s="48" t="n"/>
-      <c r="V8" s="48" t="n"/>
-      <c r="W8" s="48" t="n"/>
-      <c r="X8" s="48" t="n"/>
-      <c r="Y8" s="48" t="n"/>
-      <c r="Z8" s="48" t="n"/>
-      <c r="AA8" s="48" t="n"/>
-      <c r="AB8" s="48" t="n"/>
-      <c r="AC8" s="49" t="n"/>
+      <c r="B8" s="38" t="n"/>
+      <c r="C8" s="32" t="n"/>
+      <c r="D8" s="32" t="n"/>
+      <c r="E8" s="32" t="n"/>
+      <c r="F8" s="32" t="n"/>
+      <c r="G8" s="32" t="n"/>
+      <c r="H8" s="32" t="n"/>
+      <c r="I8" s="32" t="n"/>
+      <c r="J8" s="32" t="n"/>
+      <c r="K8" s="32" t="n"/>
+      <c r="L8" s="32" t="n"/>
+      <c r="M8" s="32" t="n"/>
+      <c r="N8" s="32" t="n"/>
+      <c r="O8" s="32" t="n"/>
+      <c r="P8" s="32" t="n"/>
+      <c r="Q8" s="32" t="n"/>
+      <c r="R8" s="32" t="n"/>
+      <c r="S8" s="32" t="n"/>
+      <c r="T8" s="32" t="n"/>
+      <c r="U8" s="32" t="n"/>
+      <c r="V8" s="32" t="n"/>
+      <c r="W8" s="32" t="n"/>
+      <c r="X8" s="32" t="n"/>
+      <c r="Y8" s="32" t="n"/>
+      <c r="Z8" s="32" t="n"/>
+      <c r="AA8" s="32" t="n"/>
+      <c r="AB8" s="32" t="n"/>
+      <c r="AC8" s="39" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>1-2.対象データ</t>
         </is>
@@ -1415,81 +1399,81 @@
     </row>
     <row r="11" ht="15" customHeight="1"/>
     <row r="13" ht="15" customHeight="1">
-      <c r="B13" s="42" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>・子供001(2020年生まれ・女)
 ・子供002(2021年生まれ・男)
 ・期間：2021年〜2026年</t>
         </is>
       </c>
-      <c r="C13" s="43" t="n"/>
-      <c r="D13" s="43" t="n"/>
-      <c r="E13" s="43" t="n"/>
-      <c r="F13" s="43" t="n"/>
-      <c r="G13" s="43" t="n"/>
-      <c r="H13" s="43" t="n"/>
-      <c r="I13" s="43" t="n"/>
-      <c r="J13" s="43" t="n"/>
-      <c r="K13" s="43" t="n"/>
-      <c r="L13" s="43" t="n"/>
-      <c r="M13" s="43" t="n"/>
-      <c r="N13" s="43" t="n"/>
-      <c r="O13" s="43" t="n"/>
-      <c r="P13" s="43" t="n"/>
-      <c r="Q13" s="43" t="n"/>
-      <c r="R13" s="43" t="n"/>
-      <c r="S13" s="43" t="n"/>
-      <c r="T13" s="43" t="n"/>
-      <c r="U13" s="43" t="n"/>
-      <c r="V13" s="43" t="n"/>
-      <c r="W13" s="43" t="n"/>
-      <c r="X13" s="43" t="n"/>
-      <c r="Y13" s="43" t="n"/>
-      <c r="Z13" s="43" t="n"/>
-      <c r="AA13" s="43" t="n"/>
-      <c r="AB13" s="43" t="n"/>
-      <c r="AC13" s="44" t="n"/>
+      <c r="C13" s="34" t="n"/>
+      <c r="D13" s="34" t="n"/>
+      <c r="E13" s="34" t="n"/>
+      <c r="F13" s="34" t="n"/>
+      <c r="G13" s="34" t="n"/>
+      <c r="H13" s="34" t="n"/>
+      <c r="I13" s="34" t="n"/>
+      <c r="J13" s="34" t="n"/>
+      <c r="K13" s="34" t="n"/>
+      <c r="L13" s="34" t="n"/>
+      <c r="M13" s="34" t="n"/>
+      <c r="N13" s="34" t="n"/>
+      <c r="O13" s="34" t="n"/>
+      <c r="P13" s="34" t="n"/>
+      <c r="Q13" s="34" t="n"/>
+      <c r="R13" s="34" t="n"/>
+      <c r="S13" s="34" t="n"/>
+      <c r="T13" s="34" t="n"/>
+      <c r="U13" s="34" t="n"/>
+      <c r="V13" s="34" t="n"/>
+      <c r="W13" s="34" t="n"/>
+      <c r="X13" s="34" t="n"/>
+      <c r="Y13" s="34" t="n"/>
+      <c r="Z13" s="34" t="n"/>
+      <c r="AA13" s="34" t="n"/>
+      <c r="AB13" s="34" t="n"/>
+      <c r="AC13" s="35" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="45" t="n"/>
-      <c r="AC14" s="46" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="AC14" s="37" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="B15" s="45" t="n"/>
-      <c r="AC15" s="46" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="AC15" s="37" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="47" t="n"/>
-      <c r="C16" s="48" t="n"/>
-      <c r="D16" s="48" t="n"/>
-      <c r="E16" s="48" t="n"/>
-      <c r="F16" s="48" t="n"/>
-      <c r="G16" s="48" t="n"/>
-      <c r="H16" s="48" t="n"/>
-      <c r="I16" s="48" t="n"/>
-      <c r="J16" s="48" t="n"/>
-      <c r="K16" s="48" t="n"/>
-      <c r="L16" s="48" t="n"/>
-      <c r="M16" s="48" t="n"/>
-      <c r="N16" s="48" t="n"/>
-      <c r="O16" s="48" t="n"/>
-      <c r="P16" s="48" t="n"/>
-      <c r="Q16" s="48" t="n"/>
-      <c r="R16" s="48" t="n"/>
-      <c r="S16" s="48" t="n"/>
-      <c r="T16" s="48" t="n"/>
-      <c r="U16" s="48" t="n"/>
-      <c r="V16" s="48" t="n"/>
-      <c r="W16" s="48" t="n"/>
-      <c r="X16" s="48" t="n"/>
-      <c r="Y16" s="48" t="n"/>
-      <c r="Z16" s="48" t="n"/>
-      <c r="AA16" s="48" t="n"/>
-      <c r="AB16" s="48" t="n"/>
-      <c r="AC16" s="49" t="n"/>
+      <c r="B16" s="38" t="n"/>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="32" t="n"/>
+      <c r="E16" s="32" t="n"/>
+      <c r="F16" s="32" t="n"/>
+      <c r="G16" s="32" t="n"/>
+      <c r="H16" s="32" t="n"/>
+      <c r="I16" s="32" t="n"/>
+      <c r="J16" s="32" t="n"/>
+      <c r="K16" s="32" t="n"/>
+      <c r="L16" s="32" t="n"/>
+      <c r="M16" s="32" t="n"/>
+      <c r="N16" s="32" t="n"/>
+      <c r="O16" s="32" t="n"/>
+      <c r="P16" s="32" t="n"/>
+      <c r="Q16" s="32" t="n"/>
+      <c r="R16" s="32" t="n"/>
+      <c r="S16" s="32" t="n"/>
+      <c r="T16" s="32" t="n"/>
+      <c r="U16" s="32" t="n"/>
+      <c r="V16" s="32" t="n"/>
+      <c r="W16" s="32" t="n"/>
+      <c r="X16" s="32" t="n"/>
+      <c r="Y16" s="32" t="n"/>
+      <c r="Z16" s="32" t="n"/>
+      <c r="AA16" s="32" t="n"/>
+      <c r="AB16" s="32" t="n"/>
+      <c r="AC16" s="39" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>1-3.使用手法</t>
         </is>
@@ -1497,7 +1481,7 @@
     </row>
     <row r="19" ht="15" customHeight="1"/>
     <row r="21" ht="15" customHeight="1">
-      <c r="B21" s="42" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>・統計分析
 ・時系列分析
@@ -1505,79 +1489,79 @@
 ・リスク予測シミュレーション</t>
         </is>
       </c>
-      <c r="C21" s="43" t="n"/>
-      <c r="D21" s="43" t="n"/>
-      <c r="E21" s="43" t="n"/>
-      <c r="F21" s="43" t="n"/>
-      <c r="G21" s="43" t="n"/>
-      <c r="H21" s="43" t="n"/>
-      <c r="I21" s="43" t="n"/>
-      <c r="J21" s="43" t="n"/>
-      <c r="K21" s="43" t="n"/>
-      <c r="L21" s="43" t="n"/>
-      <c r="M21" s="43" t="n"/>
-      <c r="N21" s="43" t="n"/>
-      <c r="O21" s="43" t="n"/>
-      <c r="P21" s="43" t="n"/>
-      <c r="Q21" s="43" t="n"/>
-      <c r="R21" s="43" t="n"/>
-      <c r="S21" s="43" t="n"/>
-      <c r="T21" s="43" t="n"/>
-      <c r="U21" s="43" t="n"/>
-      <c r="V21" s="43" t="n"/>
-      <c r="W21" s="43" t="n"/>
-      <c r="X21" s="43" t="n"/>
-      <c r="Y21" s="43" t="n"/>
-      <c r="Z21" s="43" t="n"/>
-      <c r="AA21" s="43" t="n"/>
-      <c r="AB21" s="43" t="n"/>
-      <c r="AC21" s="44" t="n"/>
+      <c r="C21" s="34" t="n"/>
+      <c r="D21" s="34" t="n"/>
+      <c r="E21" s="34" t="n"/>
+      <c r="F21" s="34" t="n"/>
+      <c r="G21" s="34" t="n"/>
+      <c r="H21" s="34" t="n"/>
+      <c r="I21" s="34" t="n"/>
+      <c r="J21" s="34" t="n"/>
+      <c r="K21" s="34" t="n"/>
+      <c r="L21" s="34" t="n"/>
+      <c r="M21" s="34" t="n"/>
+      <c r="N21" s="34" t="n"/>
+      <c r="O21" s="34" t="n"/>
+      <c r="P21" s="34" t="n"/>
+      <c r="Q21" s="34" t="n"/>
+      <c r="R21" s="34" t="n"/>
+      <c r="S21" s="34" t="n"/>
+      <c r="T21" s="34" t="n"/>
+      <c r="U21" s="34" t="n"/>
+      <c r="V21" s="34" t="n"/>
+      <c r="W21" s="34" t="n"/>
+      <c r="X21" s="34" t="n"/>
+      <c r="Y21" s="34" t="n"/>
+      <c r="Z21" s="34" t="n"/>
+      <c r="AA21" s="34" t="n"/>
+      <c r="AB21" s="34" t="n"/>
+      <c r="AC21" s="35" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="45" t="n"/>
-      <c r="AC22" s="46" t="n"/>
+      <c r="B22" s="36" t="n"/>
+      <c r="AC22" s="37" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="45" t="n"/>
-      <c r="AC23" s="46" t="n"/>
+      <c r="B23" s="36" t="n"/>
+      <c r="AC23" s="37" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="B24" s="45" t="n"/>
-      <c r="AC24" s="46" t="n"/>
+      <c r="B24" s="36" t="n"/>
+      <c r="AC24" s="37" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="B25" s="45" t="n"/>
-      <c r="AC25" s="46" t="n"/>
+      <c r="B25" s="36" t="n"/>
+      <c r="AC25" s="37" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="B26" s="47" t="n"/>
-      <c r="C26" s="48" t="n"/>
-      <c r="D26" s="48" t="n"/>
-      <c r="E26" s="48" t="n"/>
-      <c r="F26" s="48" t="n"/>
-      <c r="G26" s="48" t="n"/>
-      <c r="H26" s="48" t="n"/>
-      <c r="I26" s="48" t="n"/>
-      <c r="J26" s="48" t="n"/>
-      <c r="K26" s="48" t="n"/>
-      <c r="L26" s="48" t="n"/>
-      <c r="M26" s="48" t="n"/>
-      <c r="N26" s="48" t="n"/>
-      <c r="O26" s="48" t="n"/>
-      <c r="P26" s="48" t="n"/>
-      <c r="Q26" s="48" t="n"/>
-      <c r="R26" s="48" t="n"/>
-      <c r="S26" s="48" t="n"/>
-      <c r="T26" s="48" t="n"/>
-      <c r="U26" s="48" t="n"/>
-      <c r="V26" s="48" t="n"/>
-      <c r="W26" s="48" t="n"/>
-      <c r="X26" s="48" t="n"/>
-      <c r="Y26" s="48" t="n"/>
-      <c r="Z26" s="48" t="n"/>
-      <c r="AA26" s="48" t="n"/>
-      <c r="AB26" s="48" t="n"/>
-      <c r="AC26" s="49" t="n"/>
+      <c r="B26" s="38" t="n"/>
+      <c r="C26" s="32" t="n"/>
+      <c r="D26" s="32" t="n"/>
+      <c r="E26" s="32" t="n"/>
+      <c r="F26" s="32" t="n"/>
+      <c r="G26" s="32" t="n"/>
+      <c r="H26" s="32" t="n"/>
+      <c r="I26" s="32" t="n"/>
+      <c r="J26" s="32" t="n"/>
+      <c r="K26" s="32" t="n"/>
+      <c r="L26" s="32" t="n"/>
+      <c r="M26" s="32" t="n"/>
+      <c r="N26" s="32" t="n"/>
+      <c r="O26" s="32" t="n"/>
+      <c r="P26" s="32" t="n"/>
+      <c r="Q26" s="32" t="n"/>
+      <c r="R26" s="32" t="n"/>
+      <c r="S26" s="32" t="n"/>
+      <c r="T26" s="32" t="n"/>
+      <c r="U26" s="32" t="n"/>
+      <c r="V26" s="32" t="n"/>
+      <c r="W26" s="32" t="n"/>
+      <c r="X26" s="32" t="n"/>
+      <c r="Y26" s="32" t="n"/>
+      <c r="Z26" s="32" t="n"/>
+      <c r="AA26" s="32" t="n"/>
+      <c r="AB26" s="32" t="n"/>
+      <c r="AC26" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1599,438 +1583,466 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:AC42"/>
+  <dimension ref="B2:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="1" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>2-1.分析サマリー</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1"/>
+    <row r="4" ht="15" customHeight="1">
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>■ 主な傾向</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>■ 主な傾向</t>
-        </is>
-      </c>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="32" t="n"/>
+      <c r="H5" s="32" t="n"/>
+      <c r="I5" s="32" t="n"/>
+      <c r="J5" s="32" t="n"/>
+      <c r="K5" s="32" t="n"/>
+      <c r="L5" s="32" t="n"/>
+      <c r="M5" s="32" t="n"/>
+      <c r="N5" s="32" t="n"/>
+      <c r="O5" s="32" t="n"/>
+      <c r="P5" s="32" t="n"/>
+      <c r="Q5" s="32" t="n"/>
+      <c r="R5" s="32" t="n"/>
+      <c r="S5" s="32" t="n"/>
+      <c r="T5" s="32" t="n"/>
+      <c r="U5" s="32" t="n"/>
+      <c r="V5" s="32" t="n"/>
+      <c r="W5" s="32" t="n"/>
+      <c r="X5" s="32" t="n"/>
+      <c r="Y5" s="32" t="n"/>
+      <c r="Z5" s="32" t="n"/>
+      <c r="AA5" s="32" t="n"/>
+      <c r="AB5" s="32" t="n"/>
+      <c r="AC5" s="32" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="48" t="n"/>
-      <c r="C6" s="48" t="n"/>
-      <c r="D6" s="48" t="n"/>
-      <c r="E6" s="48" t="n"/>
-      <c r="F6" s="48" t="n"/>
-      <c r="G6" s="48" t="n"/>
-      <c r="H6" s="48" t="n"/>
-      <c r="I6" s="48" t="n"/>
-      <c r="J6" s="48" t="n"/>
-      <c r="K6" s="48" t="n"/>
-      <c r="L6" s="48" t="n"/>
-      <c r="M6" s="48" t="n"/>
-      <c r="N6" s="48" t="n"/>
-      <c r="O6" s="48" t="n"/>
-      <c r="P6" s="48" t="n"/>
-      <c r="Q6" s="48" t="n"/>
-      <c r="R6" s="48" t="n"/>
-      <c r="S6" s="48" t="n"/>
-      <c r="T6" s="48" t="n"/>
-      <c r="U6" s="48" t="n"/>
-      <c r="V6" s="48" t="n"/>
-      <c r="W6" s="48" t="n"/>
-      <c r="X6" s="48" t="n"/>
-      <c r="Y6" s="48" t="n"/>
-      <c r="Z6" s="48" t="n"/>
-      <c r="AA6" s="48" t="n"/>
-      <c r="AB6" s="48" t="n"/>
-      <c r="AC6" s="48" t="n"/>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>月齢別の平均欠席日数は約3.0～3.0日で推移しており、大きな差は認められなかった。
+学年別の平均欠席日数は約9.0～8.5日で推移しており、学年間で大きな差は認められなかった。
+登園月数別の平均欠席日数は約3.0～3.0日で推移しており、登園月数による大きな差は認められなかった。
+登園年数が短い時期の平均欠席日数は約48.5日であり、在園年数の増加とともに約3.0日まで減少した。全体で約45.5日の改善がみられ、園生活への適応や生活習慣の定着に伴い、欠席日数が減少する傾向が確認された。
+月別では1月の平均欠席日数が約22.0日と最も高く、季節性による影響が比較的強く現れていることが示唆された。
+月間平均欠席日数は約3.0～3.0日で推移しており、全体として大きな変動は認められなかった。</t>
+        </is>
+      </c>
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="34" t="n"/>
+      <c r="E6" s="34" t="n"/>
+      <c r="F6" s="34" t="n"/>
+      <c r="G6" s="34" t="n"/>
+      <c r="H6" s="34" t="n"/>
+      <c r="I6" s="34" t="n"/>
+      <c r="J6" s="34" t="n"/>
+      <c r="K6" s="34" t="n"/>
+      <c r="L6" s="34" t="n"/>
+      <c r="M6" s="34" t="n"/>
+      <c r="N6" s="34" t="n"/>
+      <c r="O6" s="34" t="n"/>
+      <c r="P6" s="34" t="n"/>
+      <c r="Q6" s="34" t="n"/>
+      <c r="R6" s="34" t="n"/>
+      <c r="S6" s="34" t="n"/>
+      <c r="T6" s="34" t="n"/>
+      <c r="U6" s="34" t="n"/>
+      <c r="V6" s="34" t="n"/>
+      <c r="W6" s="34" t="n"/>
+      <c r="X6" s="34" t="n"/>
+      <c r="Y6" s="34" t="n"/>
+      <c r="Z6" s="34" t="n"/>
+      <c r="AA6" s="34" t="n"/>
+      <c r="AB6" s="34" t="n"/>
+      <c r="AC6" s="35" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="42" t="inlineStr">
-        <is>
-          <t>月齢による大きな差は認められなかった。
-低学年ほど欠席が多く、進級に伴い安定する傾向がみられた。
-登園月数による大きな変化は認められなかった。
-登園年数が増えるにつれて欠席は減少する傾向がみられた。
-1月頃に欠席が最も多く、季節要因の影響が考えられる。
-大きな変動はみられない。</t>
-        </is>
-      </c>
-      <c r="C7" s="43" t="n"/>
-      <c r="D7" s="43" t="n"/>
-      <c r="E7" s="43" t="n"/>
-      <c r="F7" s="43" t="n"/>
-      <c r="G7" s="43" t="n"/>
-      <c r="H7" s="43" t="n"/>
-      <c r="I7" s="43" t="n"/>
-      <c r="J7" s="43" t="n"/>
-      <c r="K7" s="43" t="n"/>
-      <c r="L7" s="43" t="n"/>
-      <c r="M7" s="43" t="n"/>
-      <c r="N7" s="43" t="n"/>
-      <c r="O7" s="43" t="n"/>
-      <c r="P7" s="43" t="n"/>
-      <c r="Q7" s="43" t="n"/>
-      <c r="R7" s="43" t="n"/>
-      <c r="S7" s="43" t="n"/>
-      <c r="T7" s="43" t="n"/>
-      <c r="U7" s="43" t="n"/>
-      <c r="V7" s="43" t="n"/>
-      <c r="W7" s="43" t="n"/>
-      <c r="X7" s="43" t="n"/>
-      <c r="Y7" s="43" t="n"/>
-      <c r="Z7" s="43" t="n"/>
-      <c r="AA7" s="43" t="n"/>
-      <c r="AB7" s="43" t="n"/>
-      <c r="AC7" s="44" t="n"/>
+      <c r="B7" s="36" t="n"/>
+      <c r="AC7" s="37" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="45" t="n"/>
-      <c r="AC8" s="46" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="AC8" s="37" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="B9" s="45" t="n"/>
-      <c r="AC9" s="46" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="AC9" s="37" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="45" t="n"/>
-      <c r="AC10" s="46" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="AC10" s="37" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="B11" s="45" t="n"/>
-      <c r="AC11" s="46" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="AC11" s="37" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="B12" s="45" t="n"/>
-      <c r="AC12" s="46" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="AC12" s="37" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="B13" s="45" t="n"/>
-      <c r="AC13" s="46" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="AC13" s="37" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="45" t="n"/>
-      <c r="AC14" s="46" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="AC14" s="37" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="B15" s="45" t="n"/>
-      <c r="AC15" s="46" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="AC15" s="37" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="47" t="n"/>
-      <c r="C16" s="48" t="n"/>
-      <c r="D16" s="48" t="n"/>
-      <c r="E16" s="48" t="n"/>
-      <c r="F16" s="48" t="n"/>
-      <c r="G16" s="48" t="n"/>
-      <c r="H16" s="48" t="n"/>
-      <c r="I16" s="48" t="n"/>
-      <c r="J16" s="48" t="n"/>
-      <c r="K16" s="48" t="n"/>
-      <c r="L16" s="48" t="n"/>
-      <c r="M16" s="48" t="n"/>
-      <c r="N16" s="48" t="n"/>
-      <c r="O16" s="48" t="n"/>
-      <c r="P16" s="48" t="n"/>
-      <c r="Q16" s="48" t="n"/>
-      <c r="R16" s="48" t="n"/>
-      <c r="S16" s="48" t="n"/>
-      <c r="T16" s="48" t="n"/>
-      <c r="U16" s="48" t="n"/>
-      <c r="V16" s="48" t="n"/>
-      <c r="W16" s="48" t="n"/>
-      <c r="X16" s="48" t="n"/>
-      <c r="Y16" s="48" t="n"/>
-      <c r="Z16" s="48" t="n"/>
-      <c r="AA16" s="48" t="n"/>
-      <c r="AB16" s="48" t="n"/>
-      <c r="AC16" s="49" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="AC16" s="37" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="B17" s="36" t="n"/>
+      <c r="AC17" s="37" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="36" t="n"/>
+      <c r="AC18" s="37" t="n"/>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="B19" s="36" t="n"/>
+      <c r="AC19" s="37" t="n"/>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="B20" s="36" t="n"/>
+      <c r="AC20" s="37" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="B21" s="38" t="n"/>
+      <c r="C21" s="32" t="n"/>
+      <c r="D21" s="32" t="n"/>
+      <c r="E21" s="32" t="n"/>
+      <c r="F21" s="32" t="n"/>
+      <c r="G21" s="32" t="n"/>
+      <c r="H21" s="32" t="n"/>
+      <c r="I21" s="32" t="n"/>
+      <c r="J21" s="32" t="n"/>
+      <c r="K21" s="32" t="n"/>
+      <c r="L21" s="32" t="n"/>
+      <c r="M21" s="32" t="n"/>
+      <c r="N21" s="32" t="n"/>
+      <c r="O21" s="32" t="n"/>
+      <c r="P21" s="32" t="n"/>
+      <c r="Q21" s="32" t="n"/>
+      <c r="R21" s="32" t="n"/>
+      <c r="S21" s="32" t="n"/>
+      <c r="T21" s="32" t="n"/>
+      <c r="U21" s="32" t="n"/>
+      <c r="V21" s="32" t="n"/>
+      <c r="W21" s="32" t="n"/>
+      <c r="X21" s="32" t="n"/>
+      <c r="Y21" s="32" t="n"/>
+      <c r="Z21" s="32" t="n"/>
+      <c r="AA21" s="32" t="n"/>
+      <c r="AB21" s="32" t="n"/>
+      <c r="AC21" s="39" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>■ 未来予測結果</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="B19" s="48" t="n"/>
-      <c r="C19" s="48" t="n"/>
-      <c r="D19" s="48" t="n"/>
-      <c r="E19" s="48" t="n"/>
-      <c r="F19" s="48" t="n"/>
-      <c r="G19" s="48" t="n"/>
-      <c r="H19" s="48" t="n"/>
-      <c r="I19" s="48" t="n"/>
-      <c r="J19" s="48" t="n"/>
-      <c r="K19" s="48" t="n"/>
-      <c r="L19" s="48" t="n"/>
-      <c r="M19" s="48" t="n"/>
-      <c r="N19" s="48" t="n"/>
-      <c r="O19" s="48" t="n"/>
-      <c r="P19" s="48" t="n"/>
-      <c r="Q19" s="48" t="n"/>
-      <c r="R19" s="48" t="n"/>
-      <c r="S19" s="48" t="n"/>
-      <c r="T19" s="48" t="n"/>
-      <c r="U19" s="48" t="n"/>
-      <c r="V19" s="48" t="n"/>
-      <c r="W19" s="48" t="n"/>
-      <c r="X19" s="48" t="n"/>
-      <c r="Y19" s="48" t="n"/>
-      <c r="Z19" s="48" t="n"/>
-      <c r="AA19" s="48" t="n"/>
-      <c r="AB19" s="48" t="n"/>
-      <c r="AC19" s="48" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="B20" s="42" t="inlineStr">
-        <is>
-          <t>AI（LightGBM）による未来予測の結果、以下の見通しが得られました。
-・子供001: 予測期間中に明瞭な安定期に至らない可能性あり。
-・子供002: 予測期間中に明瞭な安定期に至らない可能性あり。</t>
-        </is>
-      </c>
-      <c r="C20" s="43" t="n"/>
-      <c r="D20" s="43" t="n"/>
-      <c r="E20" s="43" t="n"/>
-      <c r="F20" s="43" t="n"/>
-      <c r="G20" s="43" t="n"/>
-      <c r="H20" s="43" t="n"/>
-      <c r="I20" s="43" t="n"/>
-      <c r="J20" s="43" t="n"/>
-      <c r="K20" s="43" t="n"/>
-      <c r="L20" s="43" t="n"/>
-      <c r="M20" s="43" t="n"/>
-      <c r="N20" s="43" t="n"/>
-      <c r="O20" s="43" t="n"/>
-      <c r="P20" s="43" t="n"/>
-      <c r="Q20" s="43" t="n"/>
-      <c r="R20" s="43" t="n"/>
-      <c r="S20" s="43" t="n"/>
-      <c r="T20" s="43" t="n"/>
-      <c r="U20" s="43" t="n"/>
-      <c r="V20" s="43" t="n"/>
-      <c r="W20" s="43" t="n"/>
-      <c r="X20" s="43" t="n"/>
-      <c r="Y20" s="43" t="n"/>
-      <c r="Z20" s="43" t="n"/>
-      <c r="AA20" s="43" t="n"/>
-      <c r="AB20" s="43" t="n"/>
-      <c r="AC20" s="44" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="B21" s="45" t="n"/>
-      <c r="AC21" s="46" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="45" t="n"/>
-      <c r="AC22" s="46" t="n"/>
-    </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="45" t="n"/>
-      <c r="AC23" s="46" t="n"/>
+      <c r="B23" s="32" t="n"/>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="32" t="n"/>
+      <c r="E23" s="32" t="n"/>
+      <c r="F23" s="32" t="n"/>
+      <c r="G23" s="32" t="n"/>
+      <c r="H23" s="32" t="n"/>
+      <c r="I23" s="32" t="n"/>
+      <c r="J23" s="32" t="n"/>
+      <c r="K23" s="32" t="n"/>
+      <c r="L23" s="32" t="n"/>
+      <c r="M23" s="32" t="n"/>
+      <c r="N23" s="32" t="n"/>
+      <c r="O23" s="32" t="n"/>
+      <c r="P23" s="32" t="n"/>
+      <c r="Q23" s="32" t="n"/>
+      <c r="R23" s="32" t="n"/>
+      <c r="S23" s="32" t="n"/>
+      <c r="T23" s="32" t="n"/>
+      <c r="U23" s="32" t="n"/>
+      <c r="V23" s="32" t="n"/>
+      <c r="W23" s="32" t="n"/>
+      <c r="X23" s="32" t="n"/>
+      <c r="Y23" s="32" t="n"/>
+      <c r="Z23" s="32" t="n"/>
+      <c r="AA23" s="32" t="n"/>
+      <c r="AB23" s="32" t="n"/>
+      <c r="AC23" s="32" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="B24" s="45" t="n"/>
-      <c r="AC24" s="46" t="n"/>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>AI（LightGBM回帰モデル）による24か月先までの未来予測を実施した結果、以下の見通しが得られました。
+・子供001：予測期間中の平均欠席日数は約3.2日（3.2～3.2日）と推定された。予測期間内では安定基準に達しない可能性が示された。
+・子供002：予測期間中の平均欠席日数は約2.0日（2.0～2.0日）と推定された。予測期間内では安定基準に達しない可能性が示された。</t>
+        </is>
+      </c>
+      <c r="C24" s="34" t="n"/>
+      <c r="D24" s="34" t="n"/>
+      <c r="E24" s="34" t="n"/>
+      <c r="F24" s="34" t="n"/>
+      <c r="G24" s="34" t="n"/>
+      <c r="H24" s="34" t="n"/>
+      <c r="I24" s="34" t="n"/>
+      <c r="J24" s="34" t="n"/>
+      <c r="K24" s="34" t="n"/>
+      <c r="L24" s="34" t="n"/>
+      <c r="M24" s="34" t="n"/>
+      <c r="N24" s="34" t="n"/>
+      <c r="O24" s="34" t="n"/>
+      <c r="P24" s="34" t="n"/>
+      <c r="Q24" s="34" t="n"/>
+      <c r="R24" s="34" t="n"/>
+      <c r="S24" s="34" t="n"/>
+      <c r="T24" s="34" t="n"/>
+      <c r="U24" s="34" t="n"/>
+      <c r="V24" s="34" t="n"/>
+      <c r="W24" s="34" t="n"/>
+      <c r="X24" s="34" t="n"/>
+      <c r="Y24" s="34" t="n"/>
+      <c r="Z24" s="34" t="n"/>
+      <c r="AA24" s="34" t="n"/>
+      <c r="AB24" s="34" t="n"/>
+      <c r="AC24" s="35" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="B25" s="45" t="n"/>
-      <c r="AC25" s="46" t="n"/>
+      <c r="B25" s="36" t="n"/>
+      <c r="AC25" s="37" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="B26" s="45" t="n"/>
-      <c r="AC26" s="46" t="n"/>
+      <c r="B26" s="36" t="n"/>
+      <c r="AC26" s="37" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="B27" s="45" t="n"/>
-      <c r="AC27" s="46" t="n"/>
+      <c r="B27" s="36" t="n"/>
+      <c r="AC27" s="37" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="B28" s="45" t="n"/>
-      <c r="AC28" s="46" t="n"/>
+      <c r="B28" s="36" t="n"/>
+      <c r="AC28" s="37" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="47" t="n"/>
-      <c r="C29" s="48" t="n"/>
-      <c r="D29" s="48" t="n"/>
-      <c r="E29" s="48" t="n"/>
-      <c r="F29" s="48" t="n"/>
-      <c r="G29" s="48" t="n"/>
-      <c r="H29" s="48" t="n"/>
-      <c r="I29" s="48" t="n"/>
-      <c r="J29" s="48" t="n"/>
-      <c r="K29" s="48" t="n"/>
-      <c r="L29" s="48" t="n"/>
-      <c r="M29" s="48" t="n"/>
-      <c r="N29" s="48" t="n"/>
-      <c r="O29" s="48" t="n"/>
-      <c r="P29" s="48" t="n"/>
-      <c r="Q29" s="48" t="n"/>
-      <c r="R29" s="48" t="n"/>
-      <c r="S29" s="48" t="n"/>
-      <c r="T29" s="48" t="n"/>
-      <c r="U29" s="48" t="n"/>
-      <c r="V29" s="48" t="n"/>
-      <c r="W29" s="48" t="n"/>
-      <c r="X29" s="48" t="n"/>
-      <c r="Y29" s="48" t="n"/>
-      <c r="Z29" s="48" t="n"/>
-      <c r="AA29" s="48" t="n"/>
-      <c r="AB29" s="48" t="n"/>
-      <c r="AC29" s="49" t="n"/>
+      <c r="B29" s="36" t="n"/>
+      <c r="AC29" s="37" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="B30" s="36" t="n"/>
+      <c r="AC30" s="37" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="38" t="n"/>
+      <c r="C31" s="32" t="n"/>
+      <c r="D31" s="32" t="n"/>
+      <c r="E31" s="32" t="n"/>
+      <c r="F31" s="32" t="n"/>
+      <c r="G31" s="32" t="n"/>
+      <c r="H31" s="32" t="n"/>
+      <c r="I31" s="32" t="n"/>
+      <c r="J31" s="32" t="n"/>
+      <c r="K31" s="32" t="n"/>
+      <c r="L31" s="32" t="n"/>
+      <c r="M31" s="32" t="n"/>
+      <c r="N31" s="32" t="n"/>
+      <c r="O31" s="32" t="n"/>
+      <c r="P31" s="32" t="n"/>
+      <c r="Q31" s="32" t="n"/>
+      <c r="R31" s="32" t="n"/>
+      <c r="S31" s="32" t="n"/>
+      <c r="T31" s="32" t="n"/>
+      <c r="U31" s="32" t="n"/>
+      <c r="V31" s="32" t="n"/>
+      <c r="W31" s="32" t="n"/>
+      <c r="X31" s="32" t="n"/>
+      <c r="Y31" s="32" t="n"/>
+      <c r="Z31" s="32" t="n"/>
+      <c r="AA31" s="32" t="n"/>
+      <c r="AB31" s="32" t="n"/>
+      <c r="AC31" s="39" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="B33" s="30" t="inlineStr">
         <is>
           <t>■ 業務への示唆</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="B32" s="48" t="n"/>
-      <c r="C32" s="48" t="n"/>
-      <c r="D32" s="48" t="n"/>
-      <c r="E32" s="48" t="n"/>
-      <c r="F32" s="48" t="n"/>
-      <c r="G32" s="48" t="n"/>
-      <c r="H32" s="48" t="n"/>
-      <c r="I32" s="48" t="n"/>
-      <c r="J32" s="48" t="n"/>
-      <c r="K32" s="48" t="n"/>
-      <c r="L32" s="48" t="n"/>
-      <c r="M32" s="48" t="n"/>
-      <c r="N32" s="48" t="n"/>
-      <c r="O32" s="48" t="n"/>
-      <c r="P32" s="48" t="n"/>
-      <c r="Q32" s="48" t="n"/>
-      <c r="R32" s="48" t="n"/>
-      <c r="S32" s="48" t="n"/>
-      <c r="T32" s="48" t="n"/>
-      <c r="U32" s="48" t="n"/>
-      <c r="V32" s="48" t="n"/>
-      <c r="W32" s="48" t="n"/>
-      <c r="X32" s="48" t="n"/>
-      <c r="Y32" s="48" t="n"/>
-      <c r="Z32" s="48" t="n"/>
-      <c r="AA32" s="48" t="n"/>
-      <c r="AB32" s="48" t="n"/>
-      <c r="AC32" s="48" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="B33" s="42" t="inlineStr">
-        <is>
-          <t>【業務への示唆・改善提案】
-欠席リスクが高いとされる年齢・時期・季節に重点的な感染対策を実施し、家庭との情報共有をリアルタイムで強化することで、園全体の欠席日数の低減を目指します。
-子供001は明瞭な安定期に至らない可能性があり、継続的な健康観察と家庭連携が望ましい。
-子供002は明瞭な安定期に至らない可能性があり、継続的な健康観察と家庭連携が望ましい。</t>
-        </is>
-      </c>
-      <c r="C33" s="43" t="n"/>
-      <c r="D33" s="43" t="n"/>
-      <c r="E33" s="43" t="n"/>
-      <c r="F33" s="43" t="n"/>
-      <c r="G33" s="43" t="n"/>
-      <c r="H33" s="43" t="n"/>
-      <c r="I33" s="43" t="n"/>
-      <c r="J33" s="43" t="n"/>
-      <c r="K33" s="43" t="n"/>
-      <c r="L33" s="43" t="n"/>
-      <c r="M33" s="43" t="n"/>
-      <c r="N33" s="43" t="n"/>
-      <c r="O33" s="43" t="n"/>
-      <c r="P33" s="43" t="n"/>
-      <c r="Q33" s="43" t="n"/>
-      <c r="R33" s="43" t="n"/>
-      <c r="S33" s="43" t="n"/>
-      <c r="T33" s="43" t="n"/>
-      <c r="U33" s="43" t="n"/>
-      <c r="V33" s="43" t="n"/>
-      <c r="W33" s="43" t="n"/>
-      <c r="X33" s="43" t="n"/>
-      <c r="Y33" s="43" t="n"/>
-      <c r="Z33" s="43" t="n"/>
-      <c r="AA33" s="43" t="n"/>
-      <c r="AB33" s="43" t="n"/>
-      <c r="AC33" s="44" t="n"/>
-    </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="B34" s="45" t="n"/>
-      <c r="AC34" s="46" t="n"/>
+      <c r="B34" s="32" t="n"/>
+      <c r="C34" s="32" t="n"/>
+      <c r="D34" s="32" t="n"/>
+      <c r="E34" s="32" t="n"/>
+      <c r="F34" s="32" t="n"/>
+      <c r="G34" s="32" t="n"/>
+      <c r="H34" s="32" t="n"/>
+      <c r="I34" s="32" t="n"/>
+      <c r="J34" s="32" t="n"/>
+      <c r="K34" s="32" t="n"/>
+      <c r="L34" s="32" t="n"/>
+      <c r="M34" s="32" t="n"/>
+      <c r="N34" s="32" t="n"/>
+      <c r="O34" s="32" t="n"/>
+      <c r="P34" s="32" t="n"/>
+      <c r="Q34" s="32" t="n"/>
+      <c r="R34" s="32" t="n"/>
+      <c r="S34" s="32" t="n"/>
+      <c r="T34" s="32" t="n"/>
+      <c r="U34" s="32" t="n"/>
+      <c r="V34" s="32" t="n"/>
+      <c r="W34" s="32" t="n"/>
+      <c r="X34" s="32" t="n"/>
+      <c r="Y34" s="32" t="n"/>
+      <c r="Z34" s="32" t="n"/>
+      <c r="AA34" s="32" t="n"/>
+      <c r="AB34" s="32" t="n"/>
+      <c r="AC34" s="32" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="B35" s="45" t="n"/>
-      <c r="AC35" s="46" t="n"/>
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>過去データおよびAI予測結果を踏まえると、年齢や登園初期、季節要因によって欠席日数が増加する傾向が確認された。
+これらの時期には感染症対策や健康観察を強化するとともに、家庭との情報共有を継続することが重要である。
+・子供001：平均欠席日数は約3.2日と予測され、予測期間内では安定基準への到達が見込まれなかった。健康観察を継続するとともに、家庭との情報共有や個別支援を強化することが望ましい。
+・子供002：平均欠席日数は約2.0日と予測され、予測期間内では安定基準への到達が見込まれなかった。健康観察を継続するとともに、家庭との情報共有や個別支援を強化することが望ましい。</t>
+        </is>
+      </c>
+      <c r="C35" s="34" t="n"/>
+      <c r="D35" s="34" t="n"/>
+      <c r="E35" s="34" t="n"/>
+      <c r="F35" s="34" t="n"/>
+      <c r="G35" s="34" t="n"/>
+      <c r="H35" s="34" t="n"/>
+      <c r="I35" s="34" t="n"/>
+      <c r="J35" s="34" t="n"/>
+      <c r="K35" s="34" t="n"/>
+      <c r="L35" s="34" t="n"/>
+      <c r="M35" s="34" t="n"/>
+      <c r="N35" s="34" t="n"/>
+      <c r="O35" s="34" t="n"/>
+      <c r="P35" s="34" t="n"/>
+      <c r="Q35" s="34" t="n"/>
+      <c r="R35" s="34" t="n"/>
+      <c r="S35" s="34" t="n"/>
+      <c r="T35" s="34" t="n"/>
+      <c r="U35" s="34" t="n"/>
+      <c r="V35" s="34" t="n"/>
+      <c r="W35" s="34" t="n"/>
+      <c r="X35" s="34" t="n"/>
+      <c r="Y35" s="34" t="n"/>
+      <c r="Z35" s="34" t="n"/>
+      <c r="AA35" s="34" t="n"/>
+      <c r="AB35" s="34" t="n"/>
+      <c r="AC35" s="35" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="B36" s="45" t="n"/>
-      <c r="AC36" s="46" t="n"/>
+      <c r="B36" s="36" t="n"/>
+      <c r="AC36" s="37" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="B37" s="45" t="n"/>
-      <c r="AC37" s="46" t="n"/>
+      <c r="B37" s="36" t="n"/>
+      <c r="AC37" s="37" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="B38" s="45" t="n"/>
-      <c r="AC38" s="46" t="n"/>
+      <c r="B38" s="36" t="n"/>
+      <c r="AC38" s="37" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="B39" s="45" t="n"/>
-      <c r="AC39" s="46" t="n"/>
+      <c r="B39" s="36" t="n"/>
+      <c r="AC39" s="37" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="B40" s="45" t="n"/>
-      <c r="AC40" s="46" t="n"/>
+      <c r="B40" s="36" t="n"/>
+      <c r="AC40" s="37" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="B41" s="45" t="n"/>
-      <c r="AC41" s="46" t="n"/>
+      <c r="B41" s="36" t="n"/>
+      <c r="AC41" s="37" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="B42" s="47" t="n"/>
-      <c r="C42" s="48" t="n"/>
-      <c r="D42" s="48" t="n"/>
-      <c r="E42" s="48" t="n"/>
-      <c r="F42" s="48" t="n"/>
-      <c r="G42" s="48" t="n"/>
-      <c r="H42" s="48" t="n"/>
-      <c r="I42" s="48" t="n"/>
-      <c r="J42" s="48" t="n"/>
-      <c r="K42" s="48" t="n"/>
-      <c r="L42" s="48" t="n"/>
-      <c r="M42" s="48" t="n"/>
-      <c r="N42" s="48" t="n"/>
-      <c r="O42" s="48" t="n"/>
-      <c r="P42" s="48" t="n"/>
-      <c r="Q42" s="48" t="n"/>
-      <c r="R42" s="48" t="n"/>
-      <c r="S42" s="48" t="n"/>
-      <c r="T42" s="48" t="n"/>
-      <c r="U42" s="48" t="n"/>
-      <c r="V42" s="48" t="n"/>
-      <c r="W42" s="48" t="n"/>
-      <c r="X42" s="48" t="n"/>
-      <c r="Y42" s="48" t="n"/>
-      <c r="Z42" s="48" t="n"/>
-      <c r="AA42" s="48" t="n"/>
-      <c r="AB42" s="48" t="n"/>
-      <c r="AC42" s="49" t="n"/>
+      <c r="B42" s="36" t="n"/>
+      <c r="AC42" s="37" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="B43" s="36" t="n"/>
+      <c r="AC43" s="37" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="B44" s="36" t="n"/>
+      <c r="AC44" s="37" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="B45" s="36" t="n"/>
+      <c r="AC45" s="37" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="B46" s="36" t="n"/>
+      <c r="AC46" s="37" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="B47" s="38" t="n"/>
+      <c r="C47" s="32" t="n"/>
+      <c r="D47" s="32" t="n"/>
+      <c r="E47" s="32" t="n"/>
+      <c r="F47" s="32" t="n"/>
+      <c r="G47" s="32" t="n"/>
+      <c r="H47" s="32" t="n"/>
+      <c r="I47" s="32" t="n"/>
+      <c r="J47" s="32" t="n"/>
+      <c r="K47" s="32" t="n"/>
+      <c r="L47" s="32" t="n"/>
+      <c r="M47" s="32" t="n"/>
+      <c r="N47" s="32" t="n"/>
+      <c r="O47" s="32" t="n"/>
+      <c r="P47" s="32" t="n"/>
+      <c r="Q47" s="32" t="n"/>
+      <c r="R47" s="32" t="n"/>
+      <c r="S47" s="32" t="n"/>
+      <c r="T47" s="32" t="n"/>
+      <c r="U47" s="32" t="n"/>
+      <c r="V47" s="32" t="n"/>
+      <c r="W47" s="32" t="n"/>
+      <c r="X47" s="32" t="n"/>
+      <c r="Y47" s="32" t="n"/>
+      <c r="Z47" s="32" t="n"/>
+      <c r="AA47" s="32" t="n"/>
+      <c r="AB47" s="32" t="n"/>
+      <c r="AC47" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="B22:AC23"/>
     <mergeCell ref="B2:AC3"/>
-    <mergeCell ref="B20:AC29"/>
-    <mergeCell ref="B5:AC6"/>
-    <mergeCell ref="B33:AC42"/>
-    <mergeCell ref="B7:AC16"/>
-    <mergeCell ref="B31:AC32"/>
-    <mergeCell ref="B18:AC19"/>
+    <mergeCell ref="B24:AC31"/>
+    <mergeCell ref="B33:AC34"/>
+    <mergeCell ref="B6:AC21"/>
+    <mergeCell ref="B35:AC47"/>
+    <mergeCell ref="B4:AC5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" scale="99"/>
@@ -2046,11 +2058,11 @@
   <dimension ref="B2:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="1" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>2-2.分析① 月齢別</t>
         </is>
@@ -2058,7 +2070,7 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="25" ht="15" customHeight="1">
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>2-2.分析② 学年別</t>
         </is>
@@ -2085,11 +2097,11 @@
   <dimension ref="B2:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="1" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>2-2.分析③ 登園月数</t>
         </is>
@@ -2097,7 +2109,7 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="25" ht="15" customHeight="1">
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>2-2.分析④ 登園年数別</t>
         </is>
@@ -2124,11 +2136,11 @@
   <dimension ref="B2:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="1" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>2-2.分析⑤ 月間</t>
         </is>
@@ -2136,7 +2148,7 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="25" ht="15" customHeight="1">
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>2-2.分析⑥ 月別</t>
         </is>
@@ -2160,14 +2172,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:AC35"/>
+  <dimension ref="B2:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="1" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>2-2.分析 傾向考察</t>
         </is>
@@ -2175,313 +2187,353 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="4" ht="15" customHeight="1">
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>■ 考察</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="48" t="n"/>
-      <c r="C5" s="48" t="n"/>
-      <c r="D5" s="48" t="n"/>
-      <c r="E5" s="48" t="n"/>
-      <c r="F5" s="48" t="n"/>
-      <c r="G5" s="48" t="n"/>
-      <c r="H5" s="48" t="n"/>
-      <c r="I5" s="48" t="n"/>
-      <c r="J5" s="48" t="n"/>
-      <c r="K5" s="48" t="n"/>
-      <c r="L5" s="48" t="n"/>
-      <c r="M5" s="48" t="n"/>
-      <c r="N5" s="48" t="n"/>
-      <c r="O5" s="48" t="n"/>
-      <c r="P5" s="48" t="n"/>
-      <c r="Q5" s="48" t="n"/>
-      <c r="R5" s="48" t="n"/>
-      <c r="S5" s="48" t="n"/>
-      <c r="T5" s="48" t="n"/>
-      <c r="U5" s="48" t="n"/>
-      <c r="V5" s="48" t="n"/>
-      <c r="W5" s="48" t="n"/>
-      <c r="X5" s="48" t="n"/>
-      <c r="Y5" s="48" t="n"/>
-      <c r="Z5" s="48" t="n"/>
-      <c r="AA5" s="48" t="n"/>
-      <c r="AB5" s="48" t="n"/>
-      <c r="AC5" s="48" t="n"/>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="32" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="32" t="n"/>
+      <c r="H5" s="32" t="n"/>
+      <c r="I5" s="32" t="n"/>
+      <c r="J5" s="32" t="n"/>
+      <c r="K5" s="32" t="n"/>
+      <c r="L5" s="32" t="n"/>
+      <c r="M5" s="32" t="n"/>
+      <c r="N5" s="32" t="n"/>
+      <c r="O5" s="32" t="n"/>
+      <c r="P5" s="32" t="n"/>
+      <c r="Q5" s="32" t="n"/>
+      <c r="R5" s="32" t="n"/>
+      <c r="S5" s="32" t="n"/>
+      <c r="T5" s="32" t="n"/>
+      <c r="U5" s="32" t="n"/>
+      <c r="V5" s="32" t="n"/>
+      <c r="W5" s="32" t="n"/>
+      <c r="X5" s="32" t="n"/>
+      <c r="Y5" s="32" t="n"/>
+      <c r="Z5" s="32" t="n"/>
+      <c r="AA5" s="32" t="n"/>
+      <c r="AB5" s="32" t="n"/>
+      <c r="AC5" s="32" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="42" t="inlineStr">
-        <is>
-          <t>月齢による大きな差は認められなかった。
-低学年ほど欠席が多く、進級に伴い安定する傾向がみられた。
-登園月数による大きな変化は認められなかった。
-登園年数が増えるにつれて欠席は減少する傾向がみられた。
-1月頃に欠席が最も多く、季節要因の影響が考えられる。
-大きな変動はみられない。</t>
-        </is>
-      </c>
-      <c r="C6" s="43" t="n"/>
-      <c r="D6" s="43" t="n"/>
-      <c r="E6" s="43" t="n"/>
-      <c r="F6" s="43" t="n"/>
-      <c r="G6" s="43" t="n"/>
-      <c r="H6" s="43" t="n"/>
-      <c r="I6" s="43" t="n"/>
-      <c r="J6" s="43" t="n"/>
-      <c r="K6" s="43" t="n"/>
-      <c r="L6" s="43" t="n"/>
-      <c r="M6" s="43" t="n"/>
-      <c r="N6" s="43" t="n"/>
-      <c r="O6" s="43" t="n"/>
-      <c r="P6" s="43" t="n"/>
-      <c r="Q6" s="43" t="n"/>
-      <c r="R6" s="43" t="n"/>
-      <c r="S6" s="43" t="n"/>
-      <c r="T6" s="43" t="n"/>
-      <c r="U6" s="43" t="n"/>
-      <c r="V6" s="43" t="n"/>
-      <c r="W6" s="43" t="n"/>
-      <c r="X6" s="43" t="n"/>
-      <c r="Y6" s="43" t="n"/>
-      <c r="Z6" s="43" t="n"/>
-      <c r="AA6" s="43" t="n"/>
-      <c r="AB6" s="43" t="n"/>
-      <c r="AC6" s="44" t="n"/>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>月齢別の平均欠席日数は約3.0～3.0日で推移しており、大きな差は認められなかった。
+学年別の平均欠席日数は約9.0～8.5日で推移しており、学年間で大きな差は認められなかった。
+登園月数別の平均欠席日数は約3.0～3.0日で推移しており、登園月数による大きな差は認められなかった。
+登園年数が短い時期の平均欠席日数は約48.5日であり、在園年数の増加とともに約3.0日まで減少した。全体で約45.5日の改善がみられ、園生活への適応や生活習慣の定着に伴い、欠席日数が減少する傾向が確認された。
+月別では1月の平均欠席日数が約22.0日と最も高く、季節性による影響が比較的強く現れていることが示唆された。
+月間平均欠席日数は約3.0～3.0日で推移しており、全体として大きな変動は認められなかった。</t>
+        </is>
+      </c>
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="34" t="n"/>
+      <c r="E6" s="34" t="n"/>
+      <c r="F6" s="34" t="n"/>
+      <c r="G6" s="34" t="n"/>
+      <c r="H6" s="34" t="n"/>
+      <c r="I6" s="34" t="n"/>
+      <c r="J6" s="34" t="n"/>
+      <c r="K6" s="34" t="n"/>
+      <c r="L6" s="34" t="n"/>
+      <c r="M6" s="34" t="n"/>
+      <c r="N6" s="34" t="n"/>
+      <c r="O6" s="34" t="n"/>
+      <c r="P6" s="34" t="n"/>
+      <c r="Q6" s="34" t="n"/>
+      <c r="R6" s="34" t="n"/>
+      <c r="S6" s="34" t="n"/>
+      <c r="T6" s="34" t="n"/>
+      <c r="U6" s="34" t="n"/>
+      <c r="V6" s="34" t="n"/>
+      <c r="W6" s="34" t="n"/>
+      <c r="X6" s="34" t="n"/>
+      <c r="Y6" s="34" t="n"/>
+      <c r="Z6" s="34" t="n"/>
+      <c r="AA6" s="34" t="n"/>
+      <c r="AB6" s="34" t="n"/>
+      <c r="AC6" s="35" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="45" t="n"/>
-      <c r="AC7" s="46" t="n"/>
+      <c r="B7" s="36" t="n"/>
+      <c r="AC7" s="37" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="45" t="n"/>
-      <c r="AC8" s="46" t="n"/>
+      <c r="B8" s="36" t="n"/>
+      <c r="AC8" s="37" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="B9" s="45" t="n"/>
-      <c r="AC9" s="46" t="n"/>
+      <c r="B9" s="36" t="n"/>
+      <c r="AC9" s="37" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="45" t="n"/>
-      <c r="AC10" s="46" t="n"/>
+      <c r="B10" s="36" t="n"/>
+      <c r="AC10" s="37" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="B11" s="45" t="n"/>
-      <c r="AC11" s="46" t="n"/>
+      <c r="B11" s="36" t="n"/>
+      <c r="AC11" s="37" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="B12" s="45" t="n"/>
-      <c r="AC12" s="46" t="n"/>
+      <c r="B12" s="36" t="n"/>
+      <c r="AC12" s="37" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="B13" s="45" t="n"/>
-      <c r="AC13" s="46" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="AC13" s="37" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="47" t="n"/>
-      <c r="C14" s="48" t="n"/>
-      <c r="D14" s="48" t="n"/>
-      <c r="E14" s="48" t="n"/>
-      <c r="F14" s="48" t="n"/>
-      <c r="G14" s="48" t="n"/>
-      <c r="H14" s="48" t="n"/>
-      <c r="I14" s="48" t="n"/>
-      <c r="J14" s="48" t="n"/>
-      <c r="K14" s="48" t="n"/>
-      <c r="L14" s="48" t="n"/>
-      <c r="M14" s="48" t="n"/>
-      <c r="N14" s="48" t="n"/>
-      <c r="O14" s="48" t="n"/>
-      <c r="P14" s="48" t="n"/>
-      <c r="Q14" s="48" t="n"/>
-      <c r="R14" s="48" t="n"/>
-      <c r="S14" s="48" t="n"/>
-      <c r="T14" s="48" t="n"/>
-      <c r="U14" s="48" t="n"/>
-      <c r="V14" s="48" t="n"/>
-      <c r="W14" s="48" t="n"/>
-      <c r="X14" s="48" t="n"/>
-      <c r="Y14" s="48" t="n"/>
-      <c r="Z14" s="48" t="n"/>
-      <c r="AA14" s="48" t="n"/>
-      <c r="AB14" s="48" t="n"/>
-      <c r="AC14" s="49" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="AC14" s="37" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="B15" s="36" t="n"/>
+      <c r="AC15" s="37" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="36" t="n"/>
+      <c r="AC16" s="37" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="B17" s="36" t="n"/>
+      <c r="AC17" s="37" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="B18" s="36" t="n"/>
+      <c r="AC18" s="37" t="n"/>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="B19" s="36" t="n"/>
+      <c r="AC19" s="37" t="n"/>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="B20" s="36" t="n"/>
+      <c r="AC20" s="37" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="B21" s="36" t="n"/>
+      <c r="AC21" s="37" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="B22" s="36" t="n"/>
+      <c r="AC22" s="37" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="B23" s="36" t="n"/>
+      <c r="AC23" s="37" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="B24" s="38" t="n"/>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="32" t="n"/>
+      <c r="E24" s="32" t="n"/>
+      <c r="F24" s="32" t="n"/>
+      <c r="G24" s="32" t="n"/>
+      <c r="H24" s="32" t="n"/>
+      <c r="I24" s="32" t="n"/>
+      <c r="J24" s="32" t="n"/>
+      <c r="K24" s="32" t="n"/>
+      <c r="L24" s="32" t="n"/>
+      <c r="M24" s="32" t="n"/>
+      <c r="N24" s="32" t="n"/>
+      <c r="O24" s="32" t="n"/>
+      <c r="P24" s="32" t="n"/>
+      <c r="Q24" s="32" t="n"/>
+      <c r="R24" s="32" t="n"/>
+      <c r="S24" s="32" t="n"/>
+      <c r="T24" s="32" t="n"/>
+      <c r="U24" s="32" t="n"/>
+      <c r="V24" s="32" t="n"/>
+      <c r="W24" s="32" t="n"/>
+      <c r="X24" s="32" t="n"/>
+      <c r="Y24" s="32" t="n"/>
+      <c r="Z24" s="32" t="n"/>
+      <c r="AA24" s="32" t="n"/>
+      <c r="AB24" s="32" t="n"/>
+      <c r="AC24" s="39" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>■ 業務改善提案</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="48" t="n"/>
-      <c r="C17" s="48" t="n"/>
-      <c r="D17" s="48" t="n"/>
-      <c r="E17" s="48" t="n"/>
-      <c r="F17" s="48" t="n"/>
-      <c r="G17" s="48" t="n"/>
-      <c r="H17" s="48" t="n"/>
-      <c r="I17" s="48" t="n"/>
-      <c r="J17" s="48" t="n"/>
-      <c r="K17" s="48" t="n"/>
-      <c r="L17" s="48" t="n"/>
-      <c r="M17" s="48" t="n"/>
-      <c r="N17" s="48" t="n"/>
-      <c r="O17" s="48" t="n"/>
-      <c r="P17" s="48" t="n"/>
-      <c r="Q17" s="48" t="n"/>
-      <c r="R17" s="48" t="n"/>
-      <c r="S17" s="48" t="n"/>
-      <c r="T17" s="48" t="n"/>
-      <c r="U17" s="48" t="n"/>
-      <c r="V17" s="48" t="n"/>
-      <c r="W17" s="48" t="n"/>
-      <c r="X17" s="48" t="n"/>
-      <c r="Y17" s="48" t="n"/>
-      <c r="Z17" s="48" t="n"/>
-      <c r="AA17" s="48" t="n"/>
-      <c r="AB17" s="48" t="n"/>
-      <c r="AC17" s="48" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="42" t="inlineStr">
-        <is>
-          <t>【業務への示唆・改善提案】
-欠席リスクが高いとされる年齢・時期・季節に重点的な感染対策を実施し、家庭との情報共有をリアルタイムで強化することで、園全体の欠席日数の低減を目指します。
-子供001は明瞭な安定期に至らない可能性があり、継続的な健康観察と家庭連携が望ましい。
-子供002は明瞭な安定期に至らない可能性があり、継続的な健康観察と家庭連携が望ましい。</t>
-        </is>
-      </c>
-      <c r="C18" s="43" t="n"/>
-      <c r="D18" s="43" t="n"/>
-      <c r="E18" s="43" t="n"/>
-      <c r="F18" s="43" t="n"/>
-      <c r="G18" s="43" t="n"/>
-      <c r="H18" s="43" t="n"/>
-      <c r="I18" s="43" t="n"/>
-      <c r="J18" s="43" t="n"/>
-      <c r="K18" s="43" t="n"/>
-      <c r="L18" s="43" t="n"/>
-      <c r="M18" s="43" t="n"/>
-      <c r="N18" s="43" t="n"/>
-      <c r="O18" s="43" t="n"/>
-      <c r="P18" s="43" t="n"/>
-      <c r="Q18" s="43" t="n"/>
-      <c r="R18" s="43" t="n"/>
-      <c r="S18" s="43" t="n"/>
-      <c r="T18" s="43" t="n"/>
-      <c r="U18" s="43" t="n"/>
-      <c r="V18" s="43" t="n"/>
-      <c r="W18" s="43" t="n"/>
-      <c r="X18" s="43" t="n"/>
-      <c r="Y18" s="43" t="n"/>
-      <c r="Z18" s="43" t="n"/>
-      <c r="AA18" s="43" t="n"/>
-      <c r="AB18" s="43" t="n"/>
-      <c r="AC18" s="44" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="B19" s="45" t="n"/>
-      <c r="AC19" s="46" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="B20" s="45" t="n"/>
-      <c r="AC20" s="46" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="B21" s="45" t="n"/>
-      <c r="AC21" s="46" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="45" t="n"/>
-      <c r="AC22" s="46" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="45" t="n"/>
-      <c r="AC23" s="46" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="B24" s="45" t="n"/>
-      <c r="AC24" s="46" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="B25" s="45" t="n"/>
-      <c r="AC25" s="46" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="B26" s="45" t="n"/>
-      <c r="AC26" s="46" t="n"/>
-    </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="B27" s="45" t="n"/>
-      <c r="AC27" s="46" t="n"/>
+      <c r="B27" s="32" t="n"/>
+      <c r="C27" s="32" t="n"/>
+      <c r="D27" s="32" t="n"/>
+      <c r="E27" s="32" t="n"/>
+      <c r="F27" s="32" t="n"/>
+      <c r="G27" s="32" t="n"/>
+      <c r="H27" s="32" t="n"/>
+      <c r="I27" s="32" t="n"/>
+      <c r="J27" s="32" t="n"/>
+      <c r="K27" s="32" t="n"/>
+      <c r="L27" s="32" t="n"/>
+      <c r="M27" s="32" t="n"/>
+      <c r="N27" s="32" t="n"/>
+      <c r="O27" s="32" t="n"/>
+      <c r="P27" s="32" t="n"/>
+      <c r="Q27" s="32" t="n"/>
+      <c r="R27" s="32" t="n"/>
+      <c r="S27" s="32" t="n"/>
+      <c r="T27" s="32" t="n"/>
+      <c r="U27" s="32" t="n"/>
+      <c r="V27" s="32" t="n"/>
+      <c r="W27" s="32" t="n"/>
+      <c r="X27" s="32" t="n"/>
+      <c r="Y27" s="32" t="n"/>
+      <c r="Z27" s="32" t="n"/>
+      <c r="AA27" s="32" t="n"/>
+      <c r="AB27" s="32" t="n"/>
+      <c r="AC27" s="32" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="B28" s="45" t="n"/>
-      <c r="AC28" s="46" t="n"/>
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>過去データおよびAI予測結果を踏まえると、年齢や登園初期、季節要因によって欠席日数が増加する傾向が確認された。
+これらの時期には感染症対策や健康観察を強化するとともに、家庭との情報共有を継続することが重要である。
+・子供001：平均欠席日数は約3.2日と予測され、予測期間内では安定基準への到達が見込まれなかった。健康観察を継続するとともに、家庭との情報共有や個別支援を強化することが望ましい。
+・子供002：平均欠席日数は約2.0日と予測され、予測期間内では安定基準への到達が見込まれなかった。健康観察を継続するとともに、家庭との情報共有や個別支援を強化することが望ましい。</t>
+        </is>
+      </c>
+      <c r="C28" s="34" t="n"/>
+      <c r="D28" s="34" t="n"/>
+      <c r="E28" s="34" t="n"/>
+      <c r="F28" s="34" t="n"/>
+      <c r="G28" s="34" t="n"/>
+      <c r="H28" s="34" t="n"/>
+      <c r="I28" s="34" t="n"/>
+      <c r="J28" s="34" t="n"/>
+      <c r="K28" s="34" t="n"/>
+      <c r="L28" s="34" t="n"/>
+      <c r="M28" s="34" t="n"/>
+      <c r="N28" s="34" t="n"/>
+      <c r="O28" s="34" t="n"/>
+      <c r="P28" s="34" t="n"/>
+      <c r="Q28" s="34" t="n"/>
+      <c r="R28" s="34" t="n"/>
+      <c r="S28" s="34" t="n"/>
+      <c r="T28" s="34" t="n"/>
+      <c r="U28" s="34" t="n"/>
+      <c r="V28" s="34" t="n"/>
+      <c r="W28" s="34" t="n"/>
+      <c r="X28" s="34" t="n"/>
+      <c r="Y28" s="34" t="n"/>
+      <c r="Z28" s="34" t="n"/>
+      <c r="AA28" s="34" t="n"/>
+      <c r="AB28" s="34" t="n"/>
+      <c r="AC28" s="35" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="45" t="n"/>
-      <c r="AC29" s="46" t="n"/>
+      <c r="B29" s="36" t="n"/>
+      <c r="AC29" s="37" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="B30" s="45" t="n"/>
-      <c r="AC30" s="46" t="n"/>
+      <c r="B30" s="36" t="n"/>
+      <c r="AC30" s="37" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="B31" s="45" t="n"/>
-      <c r="AC31" s="46" t="n"/>
+      <c r="B31" s="36" t="n"/>
+      <c r="AC31" s="37" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="B32" s="45" t="n"/>
-      <c r="AC32" s="46" t="n"/>
+      <c r="B32" s="36" t="n"/>
+      <c r="AC32" s="37" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="B33" s="45" t="n"/>
-      <c r="AC33" s="46" t="n"/>
+      <c r="B33" s="36" t="n"/>
+      <c r="AC33" s="37" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="B34" s="45" t="n"/>
-      <c r="AC34" s="46" t="n"/>
+      <c r="B34" s="36" t="n"/>
+      <c r="AC34" s="37" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="B35" s="47" t="n"/>
-      <c r="C35" s="48" t="n"/>
-      <c r="D35" s="48" t="n"/>
-      <c r="E35" s="48" t="n"/>
-      <c r="F35" s="48" t="n"/>
-      <c r="G35" s="48" t="n"/>
-      <c r="H35" s="48" t="n"/>
-      <c r="I35" s="48" t="n"/>
-      <c r="J35" s="48" t="n"/>
-      <c r="K35" s="48" t="n"/>
-      <c r="L35" s="48" t="n"/>
-      <c r="M35" s="48" t="n"/>
-      <c r="N35" s="48" t="n"/>
-      <c r="O35" s="48" t="n"/>
-      <c r="P35" s="48" t="n"/>
-      <c r="Q35" s="48" t="n"/>
-      <c r="R35" s="48" t="n"/>
-      <c r="S35" s="48" t="n"/>
-      <c r="T35" s="48" t="n"/>
-      <c r="U35" s="48" t="n"/>
-      <c r="V35" s="48" t="n"/>
-      <c r="W35" s="48" t="n"/>
-      <c r="X35" s="48" t="n"/>
-      <c r="Y35" s="48" t="n"/>
-      <c r="Z35" s="48" t="n"/>
-      <c r="AA35" s="48" t="n"/>
-      <c r="AB35" s="48" t="n"/>
-      <c r="AC35" s="49" t="n"/>
+      <c r="B35" s="36" t="n"/>
+      <c r="AC35" s="37" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="B36" s="36" t="n"/>
+      <c r="AC36" s="37" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="B37" s="36" t="n"/>
+      <c r="AC37" s="37" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="B38" s="36" t="n"/>
+      <c r="AC38" s="37" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="B39" s="36" t="n"/>
+      <c r="AC39" s="37" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="B40" s="36" t="n"/>
+      <c r="AC40" s="37" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="B41" s="36" t="n"/>
+      <c r="AC41" s="37" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="B42" s="36" t="n"/>
+      <c r="AC42" s="37" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="B43" s="36" t="n"/>
+      <c r="AC43" s="37" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="B44" s="36" t="n"/>
+      <c r="AC44" s="37" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="B45" s="38" t="n"/>
+      <c r="C45" s="32" t="n"/>
+      <c r="D45" s="32" t="n"/>
+      <c r="E45" s="32" t="n"/>
+      <c r="F45" s="32" t="n"/>
+      <c r="G45" s="32" t="n"/>
+      <c r="H45" s="32" t="n"/>
+      <c r="I45" s="32" t="n"/>
+      <c r="J45" s="32" t="n"/>
+      <c r="K45" s="32" t="n"/>
+      <c r="L45" s="32" t="n"/>
+      <c r="M45" s="32" t="n"/>
+      <c r="N45" s="32" t="n"/>
+      <c r="O45" s="32" t="n"/>
+      <c r="P45" s="32" t="n"/>
+      <c r="Q45" s="32" t="n"/>
+      <c r="R45" s="32" t="n"/>
+      <c r="S45" s="32" t="n"/>
+      <c r="T45" s="32" t="n"/>
+      <c r="U45" s="32" t="n"/>
+      <c r="V45" s="32" t="n"/>
+      <c r="W45" s="32" t="n"/>
+      <c r="X45" s="32" t="n"/>
+      <c r="Y45" s="32" t="n"/>
+      <c r="Z45" s="32" t="n"/>
+      <c r="AA45" s="32" t="n"/>
+      <c r="AB45" s="32" t="n"/>
+      <c r="AC45" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="B2:AC3"/>
-    <mergeCell ref="B16:AC17"/>
-    <mergeCell ref="B6:AC14"/>
-    <mergeCell ref="B18:AC35"/>
+    <mergeCell ref="B28:AC45"/>
+    <mergeCell ref="B26:AC27"/>
+    <mergeCell ref="B6:AC24"/>
     <mergeCell ref="B4:AC5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2498,11 +2550,11 @@
   <dimension ref="B2:AC3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="1" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>2-2.分析⑦ 未来リスク</t>
         </is>

--- a/output/reports/サンプル/サンプル2.xlsx
+++ b/output/reports/サンプル/サンプル2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="96" yWindow="312" windowWidth="11868" windowHeight="12816" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" state="visible" r:id="rId1"/>
@@ -293,104 +293,104 @@
   <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -967,7 +967,7 @@
   <dimension ref="C12:AB44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="6" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="11" ht="15" customHeight="1" thickBot="1"/>
@@ -1048,9 +1048,9 @@
       <c r="AB17" s="47" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="J44" s="11" t="inlineStr">
-        <is>
-          <t>2026/07/02</t>
+      <c r="J44" s="22" t="inlineStr">
+        <is>
+          <t>2026/07/03</t>
         </is>
       </c>
     </row>
@@ -1073,11 +1073,11 @@
   <dimension ref="B2:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="6" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>3.総合所見</t>
         </is>
@@ -1085,95 +1085,95 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="4" ht="15" customHeight="1">
-      <c r="B4" s="33" t="inlineStr">
-        <is>
-          <t>AI（LightGBM回帰モデル）による未来予測では、対象児童2名の平均予測欠席日数は月あたり約2.6日と推定された。予測期間内に安定化が見込まれる児童はいなかった。継続的な健康観察と家庭との連携を強化し、個々の状況に応じた支援を継続することが望まれる。</t>
-        </is>
-      </c>
-      <c r="C4" s="34" t="n"/>
-      <c r="D4" s="34" t="n"/>
-      <c r="E4" s="34" t="n"/>
-      <c r="F4" s="34" t="n"/>
-      <c r="G4" s="34" t="n"/>
-      <c r="H4" s="34" t="n"/>
-      <c r="I4" s="34" t="n"/>
-      <c r="J4" s="34" t="n"/>
-      <c r="K4" s="34" t="n"/>
-      <c r="L4" s="34" t="n"/>
-      <c r="M4" s="34" t="n"/>
-      <c r="N4" s="34" t="n"/>
-      <c r="O4" s="34" t="n"/>
-      <c r="P4" s="34" t="n"/>
-      <c r="Q4" s="34" t="n"/>
-      <c r="R4" s="34" t="n"/>
-      <c r="S4" s="34" t="n"/>
-      <c r="T4" s="34" t="n"/>
-      <c r="U4" s="34" t="n"/>
-      <c r="V4" s="34" t="n"/>
-      <c r="W4" s="34" t="n"/>
-      <c r="X4" s="34" t="n"/>
-      <c r="Y4" s="34" t="n"/>
-      <c r="Z4" s="34" t="n"/>
-      <c r="AA4" s="34" t="n"/>
-      <c r="AB4" s="34" t="n"/>
-      <c r="AC4" s="35" t="n"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>AIによる予測では、対象児童2名の平均欠席日数は約2.6日と推定された。予測期間内に安定化が見込まれる児童はおらず、継続的な健康観察と家庭との連携が重要と考えられる。</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n"/>
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="3" t="n"/>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3" t="n"/>
+      <c r="T4" s="3" t="n"/>
+      <c r="U4" s="3" t="n"/>
+      <c r="V4" s="3" t="n"/>
+      <c r="W4" s="3" t="n"/>
+      <c r="X4" s="3" t="n"/>
+      <c r="Y4" s="3" t="n"/>
+      <c r="Z4" s="3" t="n"/>
+      <c r="AA4" s="3" t="n"/>
+      <c r="AB4" s="3" t="n"/>
+      <c r="AC4" s="4" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="36" t="n"/>
-      <c r="AC5" s="37" t="n"/>
+      <c r="B5" s="5" t="n"/>
+      <c r="AC5" s="7" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="36" t="n"/>
-      <c r="AC6" s="37" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="AC6" s="7" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="36" t="n"/>
-      <c r="AC7" s="37" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="AC7" s="7" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="36" t="n"/>
-      <c r="AC8" s="37" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="AC8" s="7" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="B9" s="36" t="n"/>
-      <c r="AC9" s="37" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="AC9" s="7" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="36" t="n"/>
-      <c r="AC10" s="37" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="AC10" s="7" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="B11" s="38" t="n"/>
-      <c r="C11" s="32" t="n"/>
-      <c r="D11" s="32" t="n"/>
-      <c r="E11" s="32" t="n"/>
-      <c r="F11" s="32" t="n"/>
-      <c r="G11" s="32" t="n"/>
-      <c r="H11" s="32" t="n"/>
-      <c r="I11" s="32" t="n"/>
-      <c r="J11" s="32" t="n"/>
-      <c r="K11" s="32" t="n"/>
-      <c r="L11" s="32" t="n"/>
-      <c r="M11" s="32" t="n"/>
-      <c r="N11" s="32" t="n"/>
-      <c r="O11" s="32" t="n"/>
-      <c r="P11" s="32" t="n"/>
-      <c r="Q11" s="32" t="n"/>
-      <c r="R11" s="32" t="n"/>
-      <c r="S11" s="32" t="n"/>
-      <c r="T11" s="32" t="n"/>
-      <c r="U11" s="32" t="n"/>
-      <c r="V11" s="32" t="n"/>
-      <c r="W11" s="32" t="n"/>
-      <c r="X11" s="32" t="n"/>
-      <c r="Y11" s="32" t="n"/>
-      <c r="Z11" s="32" t="n"/>
-      <c r="AA11" s="32" t="n"/>
-      <c r="AB11" s="32" t="n"/>
-      <c r="AC11" s="39" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="9" t="n"/>
+      <c r="L11" s="9" t="n"/>
+      <c r="M11" s="9" t="n"/>
+      <c r="N11" s="9" t="n"/>
+      <c r="O11" s="9" t="n"/>
+      <c r="P11" s="9" t="n"/>
+      <c r="Q11" s="9" t="n"/>
+      <c r="R11" s="9" t="n"/>
+      <c r="S11" s="9" t="n"/>
+      <c r="T11" s="9" t="n"/>
+      <c r="U11" s="9" t="n"/>
+      <c r="V11" s="9" t="n"/>
+      <c r="W11" s="9" t="n"/>
+      <c r="X11" s="9" t="n"/>
+      <c r="Y11" s="9" t="n"/>
+      <c r="Z11" s="9" t="n"/>
+      <c r="AA11" s="9" t="n"/>
+      <c r="AB11" s="9" t="n"/>
+      <c r="AC11" s="10" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>4.結論</t>
         </is>
@@ -1181,92 +1181,92 @@
     </row>
     <row r="15" ht="15" customHeight="1"/>
     <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="33" t="inlineStr">
-        <is>
-          <t>AI（LightGBM回帰モデル）による予測では、予測期間内に安定化が見込まれる児童は確認されなかった。今後も継続的な健康観察や家庭との連携を行いながら、児童一人ひとりの状況に応じた支援を継続することが重要である。本システムは欠席傾向を可視化し、継続的な健康管理を支援するための参考資料として活用できる。</t>
-        </is>
-      </c>
-      <c r="C16" s="34" t="n"/>
-      <c r="D16" s="34" t="n"/>
-      <c r="E16" s="34" t="n"/>
-      <c r="F16" s="34" t="n"/>
-      <c r="G16" s="34" t="n"/>
-      <c r="H16" s="34" t="n"/>
-      <c r="I16" s="34" t="n"/>
-      <c r="J16" s="34" t="n"/>
-      <c r="K16" s="34" t="n"/>
-      <c r="L16" s="34" t="n"/>
-      <c r="M16" s="34" t="n"/>
-      <c r="N16" s="34" t="n"/>
-      <c r="O16" s="34" t="n"/>
-      <c r="P16" s="34" t="n"/>
-      <c r="Q16" s="34" t="n"/>
-      <c r="R16" s="34" t="n"/>
-      <c r="S16" s="34" t="n"/>
-      <c r="T16" s="34" t="n"/>
-      <c r="U16" s="34" t="n"/>
-      <c r="V16" s="34" t="n"/>
-      <c r="W16" s="34" t="n"/>
-      <c r="X16" s="34" t="n"/>
-      <c r="Y16" s="34" t="n"/>
-      <c r="Z16" s="34" t="n"/>
-      <c r="AA16" s="34" t="n"/>
-      <c r="AB16" s="34" t="n"/>
-      <c r="AC16" s="35" t="n"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>AI予測では予測期間内に安定化が見込まれる児童は確認されなかった。継続的な健康観察と家庭との情報共有を行いながら、個々の状況に応じた支援を継続することが望まれる。</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
+      <c r="N16" s="3" t="n"/>
+      <c r="O16" s="3" t="n"/>
+      <c r="P16" s="3" t="n"/>
+      <c r="Q16" s="3" t="n"/>
+      <c r="R16" s="3" t="n"/>
+      <c r="S16" s="3" t="n"/>
+      <c r="T16" s="3" t="n"/>
+      <c r="U16" s="3" t="n"/>
+      <c r="V16" s="3" t="n"/>
+      <c r="W16" s="3" t="n"/>
+      <c r="X16" s="3" t="n"/>
+      <c r="Y16" s="3" t="n"/>
+      <c r="Z16" s="3" t="n"/>
+      <c r="AA16" s="3" t="n"/>
+      <c r="AB16" s="3" t="n"/>
+      <c r="AC16" s="4" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="36" t="n"/>
-      <c r="AC17" s="37" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="AC17" s="7" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="36" t="n"/>
-      <c r="AC18" s="37" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="AC18" s="7" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="B19" s="36" t="n"/>
-      <c r="AC19" s="37" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="AC19" s="7" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="B20" s="36" t="n"/>
-      <c r="AC20" s="37" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="AC20" s="7" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="B21" s="36" t="n"/>
-      <c r="AC21" s="37" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="AC21" s="7" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="36" t="n"/>
-      <c r="AC22" s="37" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="AC22" s="7" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="38" t="n"/>
-      <c r="C23" s="32" t="n"/>
-      <c r="D23" s="32" t="n"/>
-      <c r="E23" s="32" t="n"/>
-      <c r="F23" s="32" t="n"/>
-      <c r="G23" s="32" t="n"/>
-      <c r="H23" s="32" t="n"/>
-      <c r="I23" s="32" t="n"/>
-      <c r="J23" s="32" t="n"/>
-      <c r="K23" s="32" t="n"/>
-      <c r="L23" s="32" t="n"/>
-      <c r="M23" s="32" t="n"/>
-      <c r="N23" s="32" t="n"/>
-      <c r="O23" s="32" t="n"/>
-      <c r="P23" s="32" t="n"/>
-      <c r="Q23" s="32" t="n"/>
-      <c r="R23" s="32" t="n"/>
-      <c r="S23" s="32" t="n"/>
-      <c r="T23" s="32" t="n"/>
-      <c r="U23" s="32" t="n"/>
-      <c r="V23" s="32" t="n"/>
-      <c r="W23" s="32" t="n"/>
-      <c r="X23" s="32" t="n"/>
-      <c r="Y23" s="32" t="n"/>
-      <c r="Z23" s="32" t="n"/>
-      <c r="AA23" s="32" t="n"/>
-      <c r="AB23" s="32" t="n"/>
-      <c r="AC23" s="39" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
+      <c r="I23" s="9" t="n"/>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="n"/>
+      <c r="L23" s="9" t="n"/>
+      <c r="M23" s="9" t="n"/>
+      <c r="N23" s="9" t="n"/>
+      <c r="O23" s="9" t="n"/>
+      <c r="P23" s="9" t="n"/>
+      <c r="Q23" s="9" t="n"/>
+      <c r="R23" s="9" t="n"/>
+      <c r="S23" s="9" t="n"/>
+      <c r="T23" s="9" t="n"/>
+      <c r="U23" s="9" t="n"/>
+      <c r="V23" s="9" t="n"/>
+      <c r="W23" s="9" t="n"/>
+      <c r="X23" s="9" t="n"/>
+      <c r="Y23" s="9" t="n"/>
+      <c r="Z23" s="9" t="n"/>
+      <c r="AA23" s="9" t="n"/>
+      <c r="AB23" s="9" t="n"/>
+      <c r="AC23" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1289,7 +1289,7 @@
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="6" min="1" max="16384"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1306,11 +1306,11 @@
   <dimension ref="B2:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="6" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>1-1.目的</t>
         </is>
@@ -1318,80 +1318,80 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>保育園における園児の欠席傾向を分析し、
 業務改善および将来リスク予測に活用する。</t>
         </is>
       </c>
-      <c r="C5" s="34" t="n"/>
-      <c r="D5" s="34" t="n"/>
-      <c r="E5" s="34" t="n"/>
-      <c r="F5" s="34" t="n"/>
-      <c r="G5" s="34" t="n"/>
-      <c r="H5" s="34" t="n"/>
-      <c r="I5" s="34" t="n"/>
-      <c r="J5" s="34" t="n"/>
-      <c r="K5" s="34" t="n"/>
-      <c r="L5" s="34" t="n"/>
-      <c r="M5" s="34" t="n"/>
-      <c r="N5" s="34" t="n"/>
-      <c r="O5" s="34" t="n"/>
-      <c r="P5" s="34" t="n"/>
-      <c r="Q5" s="34" t="n"/>
-      <c r="R5" s="34" t="n"/>
-      <c r="S5" s="34" t="n"/>
-      <c r="T5" s="34" t="n"/>
-      <c r="U5" s="34" t="n"/>
-      <c r="V5" s="34" t="n"/>
-      <c r="W5" s="34" t="n"/>
-      <c r="X5" s="34" t="n"/>
-      <c r="Y5" s="34" t="n"/>
-      <c r="Z5" s="34" t="n"/>
-      <c r="AA5" s="34" t="n"/>
-      <c r="AB5" s="34" t="n"/>
-      <c r="AC5" s="35" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="3" t="n"/>
+      <c r="T5" s="3" t="n"/>
+      <c r="U5" s="3" t="n"/>
+      <c r="V5" s="3" t="n"/>
+      <c r="W5" s="3" t="n"/>
+      <c r="X5" s="3" t="n"/>
+      <c r="Y5" s="3" t="n"/>
+      <c r="Z5" s="3" t="n"/>
+      <c r="AA5" s="3" t="n"/>
+      <c r="AB5" s="3" t="n"/>
+      <c r="AC5" s="4" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="36" t="n"/>
-      <c r="AC6" s="37" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="AC6" s="7" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="36" t="n"/>
-      <c r="AC7" s="37" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="AC7" s="7" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="38" t="n"/>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="32" t="n"/>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="32" t="n"/>
-      <c r="G8" s="32" t="n"/>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="32" t="n"/>
-      <c r="J8" s="32" t="n"/>
-      <c r="K8" s="32" t="n"/>
-      <c r="L8" s="32" t="n"/>
-      <c r="M8" s="32" t="n"/>
-      <c r="N8" s="32" t="n"/>
-      <c r="O8" s="32" t="n"/>
-      <c r="P8" s="32" t="n"/>
-      <c r="Q8" s="32" t="n"/>
-      <c r="R8" s="32" t="n"/>
-      <c r="S8" s="32" t="n"/>
-      <c r="T8" s="32" t="n"/>
-      <c r="U8" s="32" t="n"/>
-      <c r="V8" s="32" t="n"/>
-      <c r="W8" s="32" t="n"/>
-      <c r="X8" s="32" t="n"/>
-      <c r="Y8" s="32" t="n"/>
-      <c r="Z8" s="32" t="n"/>
-      <c r="AA8" s="32" t="n"/>
-      <c r="AB8" s="32" t="n"/>
-      <c r="AC8" s="39" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="n"/>
+      <c r="L8" s="9" t="n"/>
+      <c r="M8" s="9" t="n"/>
+      <c r="N8" s="9" t="n"/>
+      <c r="O8" s="9" t="n"/>
+      <c r="P8" s="9" t="n"/>
+      <c r="Q8" s="9" t="n"/>
+      <c r="R8" s="9" t="n"/>
+      <c r="S8" s="9" t="n"/>
+      <c r="T8" s="9" t="n"/>
+      <c r="U8" s="9" t="n"/>
+      <c r="V8" s="9" t="n"/>
+      <c r="W8" s="9" t="n"/>
+      <c r="X8" s="9" t="n"/>
+      <c r="Y8" s="9" t="n"/>
+      <c r="Z8" s="9" t="n"/>
+      <c r="AA8" s="9" t="n"/>
+      <c r="AB8" s="9" t="n"/>
+      <c r="AC8" s="10" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>1-2.対象データ</t>
         </is>
@@ -1399,81 +1399,81 @@
     </row>
     <row r="11" ht="15" customHeight="1"/>
     <row r="13" ht="15" customHeight="1">
-      <c r="B13" s="33" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>・子供001(2020年生まれ・女)
 ・子供002(2021年生まれ・男)
 ・期間：2021年〜2026年</t>
         </is>
       </c>
-      <c r="C13" s="34" t="n"/>
-      <c r="D13" s="34" t="n"/>
-      <c r="E13" s="34" t="n"/>
-      <c r="F13" s="34" t="n"/>
-      <c r="G13" s="34" t="n"/>
-      <c r="H13" s="34" t="n"/>
-      <c r="I13" s="34" t="n"/>
-      <c r="J13" s="34" t="n"/>
-      <c r="K13" s="34" t="n"/>
-      <c r="L13" s="34" t="n"/>
-      <c r="M13" s="34" t="n"/>
-      <c r="N13" s="34" t="n"/>
-      <c r="O13" s="34" t="n"/>
-      <c r="P13" s="34" t="n"/>
-      <c r="Q13" s="34" t="n"/>
-      <c r="R13" s="34" t="n"/>
-      <c r="S13" s="34" t="n"/>
-      <c r="T13" s="34" t="n"/>
-      <c r="U13" s="34" t="n"/>
-      <c r="V13" s="34" t="n"/>
-      <c r="W13" s="34" t="n"/>
-      <c r="X13" s="34" t="n"/>
-      <c r="Y13" s="34" t="n"/>
-      <c r="Z13" s="34" t="n"/>
-      <c r="AA13" s="34" t="n"/>
-      <c r="AB13" s="34" t="n"/>
-      <c r="AC13" s="35" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
+      <c r="O13" s="3" t="n"/>
+      <c r="P13" s="3" t="n"/>
+      <c r="Q13" s="3" t="n"/>
+      <c r="R13" s="3" t="n"/>
+      <c r="S13" s="3" t="n"/>
+      <c r="T13" s="3" t="n"/>
+      <c r="U13" s="3" t="n"/>
+      <c r="V13" s="3" t="n"/>
+      <c r="W13" s="3" t="n"/>
+      <c r="X13" s="3" t="n"/>
+      <c r="Y13" s="3" t="n"/>
+      <c r="Z13" s="3" t="n"/>
+      <c r="AA13" s="3" t="n"/>
+      <c r="AB13" s="3" t="n"/>
+      <c r="AC13" s="4" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="36" t="n"/>
-      <c r="AC14" s="37" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="AC14" s="7" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="B15" s="36" t="n"/>
-      <c r="AC15" s="37" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="AC15" s="7" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="38" t="n"/>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="32" t="n"/>
-      <c r="E16" s="32" t="n"/>
-      <c r="F16" s="32" t="n"/>
-      <c r="G16" s="32" t="n"/>
-      <c r="H16" s="32" t="n"/>
-      <c r="I16" s="32" t="n"/>
-      <c r="J16" s="32" t="n"/>
-      <c r="K16" s="32" t="n"/>
-      <c r="L16" s="32" t="n"/>
-      <c r="M16" s="32" t="n"/>
-      <c r="N16" s="32" t="n"/>
-      <c r="O16" s="32" t="n"/>
-      <c r="P16" s="32" t="n"/>
-      <c r="Q16" s="32" t="n"/>
-      <c r="R16" s="32" t="n"/>
-      <c r="S16" s="32" t="n"/>
-      <c r="T16" s="32" t="n"/>
-      <c r="U16" s="32" t="n"/>
-      <c r="V16" s="32" t="n"/>
-      <c r="W16" s="32" t="n"/>
-      <c r="X16" s="32" t="n"/>
-      <c r="Y16" s="32" t="n"/>
-      <c r="Z16" s="32" t="n"/>
-      <c r="AA16" s="32" t="n"/>
-      <c r="AB16" s="32" t="n"/>
-      <c r="AC16" s="39" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="n"/>
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="n"/>
+      <c r="L16" s="9" t="n"/>
+      <c r="M16" s="9" t="n"/>
+      <c r="N16" s="9" t="n"/>
+      <c r="O16" s="9" t="n"/>
+      <c r="P16" s="9" t="n"/>
+      <c r="Q16" s="9" t="n"/>
+      <c r="R16" s="9" t="n"/>
+      <c r="S16" s="9" t="n"/>
+      <c r="T16" s="9" t="n"/>
+      <c r="U16" s="9" t="n"/>
+      <c r="V16" s="9" t="n"/>
+      <c r="W16" s="9" t="n"/>
+      <c r="X16" s="9" t="n"/>
+      <c r="Y16" s="9" t="n"/>
+      <c r="Z16" s="9" t="n"/>
+      <c r="AA16" s="9" t="n"/>
+      <c r="AB16" s="9" t="n"/>
+      <c r="AC16" s="10" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>1-3.使用手法</t>
         </is>
@@ -1481,7 +1481,7 @@
     </row>
     <row r="19" ht="15" customHeight="1"/>
     <row r="21" ht="15" customHeight="1">
-      <c r="B21" s="33" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>・統計分析
 ・時系列分析
@@ -1489,79 +1489,79 @@
 ・リスク予測シミュレーション</t>
         </is>
       </c>
-      <c r="C21" s="34" t="n"/>
-      <c r="D21" s="34" t="n"/>
-      <c r="E21" s="34" t="n"/>
-      <c r="F21" s="34" t="n"/>
-      <c r="G21" s="34" t="n"/>
-      <c r="H21" s="34" t="n"/>
-      <c r="I21" s="34" t="n"/>
-      <c r="J21" s="34" t="n"/>
-      <c r="K21" s="34" t="n"/>
-      <c r="L21" s="34" t="n"/>
-      <c r="M21" s="34" t="n"/>
-      <c r="N21" s="34" t="n"/>
-      <c r="O21" s="34" t="n"/>
-      <c r="P21" s="34" t="n"/>
-      <c r="Q21" s="34" t="n"/>
-      <c r="R21" s="34" t="n"/>
-      <c r="S21" s="34" t="n"/>
-      <c r="T21" s="34" t="n"/>
-      <c r="U21" s="34" t="n"/>
-      <c r="V21" s="34" t="n"/>
-      <c r="W21" s="34" t="n"/>
-      <c r="X21" s="34" t="n"/>
-      <c r="Y21" s="34" t="n"/>
-      <c r="Z21" s="34" t="n"/>
-      <c r="AA21" s="34" t="n"/>
-      <c r="AB21" s="34" t="n"/>
-      <c r="AC21" s="35" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="3" t="n"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="3" t="n"/>
+      <c r="O21" s="3" t="n"/>
+      <c r="P21" s="3" t="n"/>
+      <c r="Q21" s="3" t="n"/>
+      <c r="R21" s="3" t="n"/>
+      <c r="S21" s="3" t="n"/>
+      <c r="T21" s="3" t="n"/>
+      <c r="U21" s="3" t="n"/>
+      <c r="V21" s="3" t="n"/>
+      <c r="W21" s="3" t="n"/>
+      <c r="X21" s="3" t="n"/>
+      <c r="Y21" s="3" t="n"/>
+      <c r="Z21" s="3" t="n"/>
+      <c r="AA21" s="3" t="n"/>
+      <c r="AB21" s="3" t="n"/>
+      <c r="AC21" s="4" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="36" t="n"/>
-      <c r="AC22" s="37" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="AC22" s="7" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="36" t="n"/>
-      <c r="AC23" s="37" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="AC23" s="7" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="B24" s="36" t="n"/>
-      <c r="AC24" s="37" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="AC24" s="7" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="B25" s="36" t="n"/>
-      <c r="AC25" s="37" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="AC25" s="7" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="B26" s="38" t="n"/>
-      <c r="C26" s="32" t="n"/>
-      <c r="D26" s="32" t="n"/>
-      <c r="E26" s="32" t="n"/>
-      <c r="F26" s="32" t="n"/>
-      <c r="G26" s="32" t="n"/>
-      <c r="H26" s="32" t="n"/>
-      <c r="I26" s="32" t="n"/>
-      <c r="J26" s="32" t="n"/>
-      <c r="K26" s="32" t="n"/>
-      <c r="L26" s="32" t="n"/>
-      <c r="M26" s="32" t="n"/>
-      <c r="N26" s="32" t="n"/>
-      <c r="O26" s="32" t="n"/>
-      <c r="P26" s="32" t="n"/>
-      <c r="Q26" s="32" t="n"/>
-      <c r="R26" s="32" t="n"/>
-      <c r="S26" s="32" t="n"/>
-      <c r="T26" s="32" t="n"/>
-      <c r="U26" s="32" t="n"/>
-      <c r="V26" s="32" t="n"/>
-      <c r="W26" s="32" t="n"/>
-      <c r="X26" s="32" t="n"/>
-      <c r="Y26" s="32" t="n"/>
-      <c r="Z26" s="32" t="n"/>
-      <c r="AA26" s="32" t="n"/>
-      <c r="AB26" s="32" t="n"/>
-      <c r="AC26" s="39" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="9" t="n"/>
+      <c r="I26" s="9" t="n"/>
+      <c r="J26" s="9" t="n"/>
+      <c r="K26" s="9" t="n"/>
+      <c r="L26" s="9" t="n"/>
+      <c r="M26" s="9" t="n"/>
+      <c r="N26" s="9" t="n"/>
+      <c r="O26" s="9" t="n"/>
+      <c r="P26" s="9" t="n"/>
+      <c r="Q26" s="9" t="n"/>
+      <c r="R26" s="9" t="n"/>
+      <c r="S26" s="9" t="n"/>
+      <c r="T26" s="9" t="n"/>
+      <c r="U26" s="9" t="n"/>
+      <c r="V26" s="9" t="n"/>
+      <c r="W26" s="9" t="n"/>
+      <c r="X26" s="9" t="n"/>
+      <c r="Y26" s="9" t="n"/>
+      <c r="Z26" s="9" t="n"/>
+      <c r="AA26" s="9" t="n"/>
+      <c r="AB26" s="9" t="n"/>
+      <c r="AC26" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1586,11 +1586,11 @@
   <dimension ref="B2:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="6" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>2-1.分析サマリー</t>
         </is>
@@ -1598,451 +1598,462 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="4" ht="15" customHeight="1">
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>■ 主な傾向</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="32" t="n"/>
-      <c r="C5" s="32" t="n"/>
-      <c r="D5" s="32" t="n"/>
-      <c r="E5" s="32" t="n"/>
-      <c r="F5" s="32" t="n"/>
-      <c r="G5" s="32" t="n"/>
-      <c r="H5" s="32" t="n"/>
-      <c r="I5" s="32" t="n"/>
-      <c r="J5" s="32" t="n"/>
-      <c r="K5" s="32" t="n"/>
-      <c r="L5" s="32" t="n"/>
-      <c r="M5" s="32" t="n"/>
-      <c r="N5" s="32" t="n"/>
-      <c r="O5" s="32" t="n"/>
-      <c r="P5" s="32" t="n"/>
-      <c r="Q5" s="32" t="n"/>
-      <c r="R5" s="32" t="n"/>
-      <c r="S5" s="32" t="n"/>
-      <c r="T5" s="32" t="n"/>
-      <c r="U5" s="32" t="n"/>
-      <c r="V5" s="32" t="n"/>
-      <c r="W5" s="32" t="n"/>
-      <c r="X5" s="32" t="n"/>
-      <c r="Y5" s="32" t="n"/>
-      <c r="Z5" s="32" t="n"/>
-      <c r="AA5" s="32" t="n"/>
-      <c r="AB5" s="32" t="n"/>
-      <c r="AC5" s="32" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="9" t="n"/>
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" s="9" t="n"/>
+      <c r="M5" s="9" t="n"/>
+      <c r="N5" s="9" t="n"/>
+      <c r="O5" s="9" t="n"/>
+      <c r="P5" s="9" t="n"/>
+      <c r="Q5" s="9" t="n"/>
+      <c r="R5" s="9" t="n"/>
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="9" t="n"/>
+      <c r="U5" s="9" t="n"/>
+      <c r="V5" s="9" t="n"/>
+      <c r="W5" s="9" t="n"/>
+      <c r="X5" s="9" t="n"/>
+      <c r="Y5" s="9" t="n"/>
+      <c r="Z5" s="9" t="n"/>
+      <c r="AA5" s="9" t="n"/>
+      <c r="AB5" s="9" t="n"/>
+      <c r="AC5" s="9" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="33" t="inlineStr">
-        <is>
-          <t>月齢別の平均欠席日数は約3.0～3.0日で推移しており、大きな差は認められなかった。
-学年別の平均欠席日数は約9.0～8.5日で推移しており、学年間で大きな差は認められなかった。
-登園月数別の平均欠席日数は約3.0～3.0日で推移しており、登園月数による大きな差は認められなかった。
-登園年数が短い時期の平均欠席日数は約48.5日であり、在園年数の増加とともに約3.0日まで減少した。全体で約45.5日の改善がみられ、園生活への適応や生活習慣の定着に伴い、欠席日数が減少する傾向が確認された。
-月別では1月の平均欠席日数が約22.0日と最も高く、季節性による影響が比較的強く現れていることが示唆された。
-月間平均欠席日数は約3.0～3.0日で推移しており、全体として大きな変動は認められなかった。</t>
-        </is>
-      </c>
-      <c r="C6" s="34" t="n"/>
-      <c r="D6" s="34" t="n"/>
-      <c r="E6" s="34" t="n"/>
-      <c r="F6" s="34" t="n"/>
-      <c r="G6" s="34" t="n"/>
-      <c r="H6" s="34" t="n"/>
-      <c r="I6" s="34" t="n"/>
-      <c r="J6" s="34" t="n"/>
-      <c r="K6" s="34" t="n"/>
-      <c r="L6" s="34" t="n"/>
-      <c r="M6" s="34" t="n"/>
-      <c r="N6" s="34" t="n"/>
-      <c r="O6" s="34" t="n"/>
-      <c r="P6" s="34" t="n"/>
-      <c r="Q6" s="34" t="n"/>
-      <c r="R6" s="34" t="n"/>
-      <c r="S6" s="34" t="n"/>
-      <c r="T6" s="34" t="n"/>
-      <c r="U6" s="34" t="n"/>
-      <c r="V6" s="34" t="n"/>
-      <c r="W6" s="34" t="n"/>
-      <c r="X6" s="34" t="n"/>
-      <c r="Y6" s="34" t="n"/>
-      <c r="Z6" s="34" t="n"/>
-      <c r="AA6" s="34" t="n"/>
-      <c r="AB6" s="34" t="n"/>
-      <c r="AC6" s="35" t="n"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>【子供001】
+月齢が上がるにつれて平均欠席日数は約3.0日から約5.0日へ増加した。
+学年が上がるにつれて平均欠席日数は約18.0日から約0.0日へ減少した。
+登園月数の経過に伴い平均欠席日数は約3.0日から約5.0日へ増加した。
+登園年数の経過に伴い平均欠席日数は約58.0日から約5.0日へ減少した。
+2月の平均欠席日数が約25.0日と最も高く、季節性の影響がみられた。
+月間推移では平均欠席日数が約3.0日から約5.0日へ増加した。
+【子供002】
+月齢が上がるにつれて平均欠席日数は約3.0日から約1.0日へ減少した。
+学年が上がるにつれて平均欠席日数は約0.0日から約17.0日へ増加した。
+登園月数の経過に伴い平均欠席日数は約3.0日から約1.0日へ減少した。
+登園年数の経過に伴い平均欠席日数は約39.0日から約1.0日へ減少した。
+1月の平均欠席日数が約22.0日と最も高く、季節性の影響がみられた。
+月間推移では平均欠席日数が約3.0日から約1.0日へ減少した。</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="n"/>
+      <c r="Q6" s="3" t="n"/>
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" s="3" t="n"/>
+      <c r="T6" s="3" t="n"/>
+      <c r="U6" s="3" t="n"/>
+      <c r="V6" s="3" t="n"/>
+      <c r="W6" s="3" t="n"/>
+      <c r="X6" s="3" t="n"/>
+      <c r="Y6" s="3" t="n"/>
+      <c r="Z6" s="3" t="n"/>
+      <c r="AA6" s="3" t="n"/>
+      <c r="AB6" s="3" t="n"/>
+      <c r="AC6" s="4" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="36" t="n"/>
-      <c r="AC7" s="37" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="AC7" s="7" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="36" t="n"/>
-      <c r="AC8" s="37" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="AC8" s="7" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="B9" s="36" t="n"/>
-      <c r="AC9" s="37" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="AC9" s="7" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="36" t="n"/>
-      <c r="AC10" s="37" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="AC10" s="7" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="B11" s="36" t="n"/>
-      <c r="AC11" s="37" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="AC11" s="7" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="B12" s="36" t="n"/>
-      <c r="AC12" s="37" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="AC12" s="7" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="B13" s="36" t="n"/>
-      <c r="AC13" s="37" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="AC13" s="7" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="36" t="n"/>
-      <c r="AC14" s="37" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="AC14" s="7" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="B15" s="36" t="n"/>
-      <c r="AC15" s="37" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="AC15" s="7" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="36" t="n"/>
-      <c r="AC16" s="37" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="AC16" s="7" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="36" t="n"/>
-      <c r="AC17" s="37" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="AC17" s="7" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="36" t="n"/>
-      <c r="AC18" s="37" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="AC18" s="7" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="B19" s="36" t="n"/>
-      <c r="AC19" s="37" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="AC19" s="7" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="B20" s="36" t="n"/>
-      <c r="AC20" s="37" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="AC20" s="7" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="B21" s="38" t="n"/>
-      <c r="C21" s="32" t="n"/>
-      <c r="D21" s="32" t="n"/>
-      <c r="E21" s="32" t="n"/>
-      <c r="F21" s="32" t="n"/>
-      <c r="G21" s="32" t="n"/>
-      <c r="H21" s="32" t="n"/>
-      <c r="I21" s="32" t="n"/>
-      <c r="J21" s="32" t="n"/>
-      <c r="K21" s="32" t="n"/>
-      <c r="L21" s="32" t="n"/>
-      <c r="M21" s="32" t="n"/>
-      <c r="N21" s="32" t="n"/>
-      <c r="O21" s="32" t="n"/>
-      <c r="P21" s="32" t="n"/>
-      <c r="Q21" s="32" t="n"/>
-      <c r="R21" s="32" t="n"/>
-      <c r="S21" s="32" t="n"/>
-      <c r="T21" s="32" t="n"/>
-      <c r="U21" s="32" t="n"/>
-      <c r="V21" s="32" t="n"/>
-      <c r="W21" s="32" t="n"/>
-      <c r="X21" s="32" t="n"/>
-      <c r="Y21" s="32" t="n"/>
-      <c r="Z21" s="32" t="n"/>
-      <c r="AA21" s="32" t="n"/>
-      <c r="AB21" s="32" t="n"/>
-      <c r="AC21" s="39" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="AC21" s="7" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B22" s="5" t="n"/>
+      <c r="AC22" s="7" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="B23" s="5" t="n"/>
+      <c r="AC23" s="7" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="9" t="n"/>
+      <c r="I24" s="9" t="n"/>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
+      <c r="L24" s="9" t="n"/>
+      <c r="M24" s="9" t="n"/>
+      <c r="N24" s="9" t="n"/>
+      <c r="O24" s="9" t="n"/>
+      <c r="P24" s="9" t="n"/>
+      <c r="Q24" s="9" t="n"/>
+      <c r="R24" s="9" t="n"/>
+      <c r="S24" s="9" t="n"/>
+      <c r="T24" s="9" t="n"/>
+      <c r="U24" s="9" t="n"/>
+      <c r="V24" s="9" t="n"/>
+      <c r="W24" s="9" t="n"/>
+      <c r="X24" s="9" t="n"/>
+      <c r="Y24" s="9" t="n"/>
+      <c r="Z24" s="9" t="n"/>
+      <c r="AA24" s="9" t="n"/>
+      <c r="AB24" s="9" t="n"/>
+      <c r="AC24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>■ 未来予測結果</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="32" t="n"/>
-      <c r="C23" s="32" t="n"/>
-      <c r="D23" s="32" t="n"/>
-      <c r="E23" s="32" t="n"/>
-      <c r="F23" s="32" t="n"/>
-      <c r="G23" s="32" t="n"/>
-      <c r="H23" s="32" t="n"/>
-      <c r="I23" s="32" t="n"/>
-      <c r="J23" s="32" t="n"/>
-      <c r="K23" s="32" t="n"/>
-      <c r="L23" s="32" t="n"/>
-      <c r="M23" s="32" t="n"/>
-      <c r="N23" s="32" t="n"/>
-      <c r="O23" s="32" t="n"/>
-      <c r="P23" s="32" t="n"/>
-      <c r="Q23" s="32" t="n"/>
-      <c r="R23" s="32" t="n"/>
-      <c r="S23" s="32" t="n"/>
-      <c r="T23" s="32" t="n"/>
-      <c r="U23" s="32" t="n"/>
-      <c r="V23" s="32" t="n"/>
-      <c r="W23" s="32" t="n"/>
-      <c r="X23" s="32" t="n"/>
-      <c r="Y23" s="32" t="n"/>
-      <c r="Z23" s="32" t="n"/>
-      <c r="AA23" s="32" t="n"/>
-      <c r="AB23" s="32" t="n"/>
-      <c r="AC23" s="32" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>AI（LightGBM回帰モデル）による24か月先までの未来予測を実施した結果、以下の見通しが得られました。
-・子供001：予測期間中の平均欠席日数は約3.2日（3.2～3.2日）と推定された。予測期間内では安定基準に達しない可能性が示された。
-・子供002：予測期間中の平均欠席日数は約2.0日（2.0～2.0日）と推定された。予測期間内では安定基準に達しない可能性が示された。</t>
-        </is>
-      </c>
-      <c r="C24" s="34" t="n"/>
-      <c r="D24" s="34" t="n"/>
-      <c r="E24" s="34" t="n"/>
-      <c r="F24" s="34" t="n"/>
-      <c r="G24" s="34" t="n"/>
-      <c r="H24" s="34" t="n"/>
-      <c r="I24" s="34" t="n"/>
-      <c r="J24" s="34" t="n"/>
-      <c r="K24" s="34" t="n"/>
-      <c r="L24" s="34" t="n"/>
-      <c r="M24" s="34" t="n"/>
-      <c r="N24" s="34" t="n"/>
-      <c r="O24" s="34" t="n"/>
-      <c r="P24" s="34" t="n"/>
-      <c r="Q24" s="34" t="n"/>
-      <c r="R24" s="34" t="n"/>
-      <c r="S24" s="34" t="n"/>
-      <c r="T24" s="34" t="n"/>
-      <c r="U24" s="34" t="n"/>
-      <c r="V24" s="34" t="n"/>
-      <c r="W24" s="34" t="n"/>
-      <c r="X24" s="34" t="n"/>
-      <c r="Y24" s="34" t="n"/>
-      <c r="Z24" s="34" t="n"/>
-      <c r="AA24" s="34" t="n"/>
-      <c r="AB24" s="34" t="n"/>
-      <c r="AC24" s="35" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="B25" s="36" t="n"/>
-      <c r="AC25" s="37" t="n"/>
-    </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="B26" s="36" t="n"/>
-      <c r="AC26" s="37" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="9" t="n"/>
+      <c r="I26" s="9" t="n"/>
+      <c r="J26" s="9" t="n"/>
+      <c r="K26" s="9" t="n"/>
+      <c r="L26" s="9" t="n"/>
+      <c r="M26" s="9" t="n"/>
+      <c r="N26" s="9" t="n"/>
+      <c r="O26" s="9" t="n"/>
+      <c r="P26" s="9" t="n"/>
+      <c r="Q26" s="9" t="n"/>
+      <c r="R26" s="9" t="n"/>
+      <c r="S26" s="9" t="n"/>
+      <c r="T26" s="9" t="n"/>
+      <c r="U26" s="9" t="n"/>
+      <c r="V26" s="9" t="n"/>
+      <c r="W26" s="9" t="n"/>
+      <c r="X26" s="9" t="n"/>
+      <c r="Y26" s="9" t="n"/>
+      <c r="Z26" s="9" t="n"/>
+      <c r="AA26" s="9" t="n"/>
+      <c r="AB26" s="9" t="n"/>
+      <c r="AC26" s="9" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="B27" s="36" t="n"/>
-      <c r="AC27" s="37" t="n"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>【子供001】
+平均欠席日数は約3.2日と予測された。
+予測期間内に安定基準へ到達しないと予測された。
+【子供002】
+平均欠席日数は約2.0日と予測された。
+予測期間内に安定基準へ到達しないと予測された。</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n"/>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="3" t="n"/>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="3" t="n"/>
+      <c r="O27" s="3" t="n"/>
+      <c r="P27" s="3" t="n"/>
+      <c r="Q27" s="3" t="n"/>
+      <c r="R27" s="3" t="n"/>
+      <c r="S27" s="3" t="n"/>
+      <c r="T27" s="3" t="n"/>
+      <c r="U27" s="3" t="n"/>
+      <c r="V27" s="3" t="n"/>
+      <c r="W27" s="3" t="n"/>
+      <c r="X27" s="3" t="n"/>
+      <c r="Y27" s="3" t="n"/>
+      <c r="Z27" s="3" t="n"/>
+      <c r="AA27" s="3" t="n"/>
+      <c r="AB27" s="3" t="n"/>
+      <c r="AC27" s="4" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="B28" s="36" t="n"/>
-      <c r="AC28" s="37" t="n"/>
+      <c r="B28" s="5" t="n"/>
+      <c r="AC28" s="7" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="36" t="n"/>
-      <c r="AC29" s="37" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="AC29" s="7" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="B30" s="36" t="n"/>
-      <c r="AC30" s="37" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="AC30" s="7" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="B31" s="38" t="n"/>
-      <c r="C31" s="32" t="n"/>
-      <c r="D31" s="32" t="n"/>
-      <c r="E31" s="32" t="n"/>
-      <c r="F31" s="32" t="n"/>
-      <c r="G31" s="32" t="n"/>
-      <c r="H31" s="32" t="n"/>
-      <c r="I31" s="32" t="n"/>
-      <c r="J31" s="32" t="n"/>
-      <c r="K31" s="32" t="n"/>
-      <c r="L31" s="32" t="n"/>
-      <c r="M31" s="32" t="n"/>
-      <c r="N31" s="32" t="n"/>
-      <c r="O31" s="32" t="n"/>
-      <c r="P31" s="32" t="n"/>
-      <c r="Q31" s="32" t="n"/>
-      <c r="R31" s="32" t="n"/>
-      <c r="S31" s="32" t="n"/>
-      <c r="T31" s="32" t="n"/>
-      <c r="U31" s="32" t="n"/>
-      <c r="V31" s="32" t="n"/>
-      <c r="W31" s="32" t="n"/>
-      <c r="X31" s="32" t="n"/>
-      <c r="Y31" s="32" t="n"/>
-      <c r="Z31" s="32" t="n"/>
-      <c r="AA31" s="32" t="n"/>
-      <c r="AB31" s="32" t="n"/>
-      <c r="AC31" s="39" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="AC31" s="7" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="B32" s="5" t="n"/>
+      <c r="AC32" s="7" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="B33" s="30" t="inlineStr">
+      <c r="B33" s="5" t="n"/>
+      <c r="AC33" s="7" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="B34" s="5" t="n"/>
+      <c r="AC34" s="7" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="9" t="n"/>
+      <c r="L35" s="9" t="n"/>
+      <c r="M35" s="9" t="n"/>
+      <c r="N35" s="9" t="n"/>
+      <c r="O35" s="9" t="n"/>
+      <c r="P35" s="9" t="n"/>
+      <c r="Q35" s="9" t="n"/>
+      <c r="R35" s="9" t="n"/>
+      <c r="S35" s="9" t="n"/>
+      <c r="T35" s="9" t="n"/>
+      <c r="U35" s="9" t="n"/>
+      <c r="V35" s="9" t="n"/>
+      <c r="W35" s="9" t="n"/>
+      <c r="X35" s="9" t="n"/>
+      <c r="Y35" s="9" t="n"/>
+      <c r="Z35" s="9" t="n"/>
+      <c r="AA35" s="9" t="n"/>
+      <c r="AB35" s="9" t="n"/>
+      <c r="AC35" s="10" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>■ 業務への示唆</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="B34" s="32" t="n"/>
-      <c r="C34" s="32" t="n"/>
-      <c r="D34" s="32" t="n"/>
-      <c r="E34" s="32" t="n"/>
-      <c r="F34" s="32" t="n"/>
-      <c r="G34" s="32" t="n"/>
-      <c r="H34" s="32" t="n"/>
-      <c r="I34" s="32" t="n"/>
-      <c r="J34" s="32" t="n"/>
-      <c r="K34" s="32" t="n"/>
-      <c r="L34" s="32" t="n"/>
-      <c r="M34" s="32" t="n"/>
-      <c r="N34" s="32" t="n"/>
-      <c r="O34" s="32" t="n"/>
-      <c r="P34" s="32" t="n"/>
-      <c r="Q34" s="32" t="n"/>
-      <c r="R34" s="32" t="n"/>
-      <c r="S34" s="32" t="n"/>
-      <c r="T34" s="32" t="n"/>
-      <c r="U34" s="32" t="n"/>
-      <c r="V34" s="32" t="n"/>
-      <c r="W34" s="32" t="n"/>
-      <c r="X34" s="32" t="n"/>
-      <c r="Y34" s="32" t="n"/>
-      <c r="Z34" s="32" t="n"/>
-      <c r="AA34" s="32" t="n"/>
-      <c r="AB34" s="32" t="n"/>
-      <c r="AC34" s="32" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="B35" s="33" t="inlineStr">
-        <is>
-          <t>過去データおよびAI予測結果を踏まえると、年齢や登園初期、季節要因によって欠席日数が増加する傾向が確認された。
-これらの時期には感染症対策や健康観察を強化するとともに、家庭との情報共有を継続することが重要である。
-・子供001：平均欠席日数は約3.2日と予測され、予測期間内では安定基準への到達が見込まれなかった。健康観察を継続するとともに、家庭との情報共有や個別支援を強化することが望ましい。
-・子供002：平均欠席日数は約2.0日と予測され、予測期間内では安定基準への到達が見込まれなかった。健康観察を継続するとともに、家庭との情報共有や個別支援を強化することが望ましい。</t>
-        </is>
-      </c>
-      <c r="C35" s="34" t="n"/>
-      <c r="D35" s="34" t="n"/>
-      <c r="E35" s="34" t="n"/>
-      <c r="F35" s="34" t="n"/>
-      <c r="G35" s="34" t="n"/>
-      <c r="H35" s="34" t="n"/>
-      <c r="I35" s="34" t="n"/>
-      <c r="J35" s="34" t="n"/>
-      <c r="K35" s="34" t="n"/>
-      <c r="L35" s="34" t="n"/>
-      <c r="M35" s="34" t="n"/>
-      <c r="N35" s="34" t="n"/>
-      <c r="O35" s="34" t="n"/>
-      <c r="P35" s="34" t="n"/>
-      <c r="Q35" s="34" t="n"/>
-      <c r="R35" s="34" t="n"/>
-      <c r="S35" s="34" t="n"/>
-      <c r="T35" s="34" t="n"/>
-      <c r="U35" s="34" t="n"/>
-      <c r="V35" s="34" t="n"/>
-      <c r="W35" s="34" t="n"/>
-      <c r="X35" s="34" t="n"/>
-      <c r="Y35" s="34" t="n"/>
-      <c r="Z35" s="34" t="n"/>
-      <c r="AA35" s="34" t="n"/>
-      <c r="AB35" s="34" t="n"/>
-      <c r="AC35" s="35" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="B36" s="36" t="n"/>
-      <c r="AC36" s="37" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="B37" s="36" t="n"/>
-      <c r="AC37" s="37" t="n"/>
-    </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="B38" s="36" t="n"/>
-      <c r="AC38" s="37" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
+      <c r="H38" s="9" t="n"/>
+      <c r="I38" s="9" t="n"/>
+      <c r="J38" s="9" t="n"/>
+      <c r="K38" s="9" t="n"/>
+      <c r="L38" s="9" t="n"/>
+      <c r="M38" s="9" t="n"/>
+      <c r="N38" s="9" t="n"/>
+      <c r="O38" s="9" t="n"/>
+      <c r="P38" s="9" t="n"/>
+      <c r="Q38" s="9" t="n"/>
+      <c r="R38" s="9" t="n"/>
+      <c r="S38" s="9" t="n"/>
+      <c r="T38" s="9" t="n"/>
+      <c r="U38" s="9" t="n"/>
+      <c r="V38" s="9" t="n"/>
+      <c r="W38" s="9" t="n"/>
+      <c r="X38" s="9" t="n"/>
+      <c r="Y38" s="9" t="n"/>
+      <c r="Z38" s="9" t="n"/>
+      <c r="AA38" s="9" t="n"/>
+      <c r="AB38" s="9" t="n"/>
+      <c r="AC38" s="9" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="B39" s="36" t="n"/>
-      <c r="AC39" s="37" t="n"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>【子供001】
+平均欠席日数は約3.2日と予測された。予測期間内で安定化は見込まれないため、健康観察や個別支援を継続することが望ましい。
+【子供002】
+平均欠席日数は約2.0日と予測された。予測期間内で安定化は見込まれないため、健康観察や個別支援を継続することが望ましい。</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="n"/>
+      <c r="L39" s="3" t="n"/>
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="3" t="n"/>
+      <c r="O39" s="3" t="n"/>
+      <c r="P39" s="3" t="n"/>
+      <c r="Q39" s="3" t="n"/>
+      <c r="R39" s="3" t="n"/>
+      <c r="S39" s="3" t="n"/>
+      <c r="T39" s="3" t="n"/>
+      <c r="U39" s="3" t="n"/>
+      <c r="V39" s="3" t="n"/>
+      <c r="W39" s="3" t="n"/>
+      <c r="X39" s="3" t="n"/>
+      <c r="Y39" s="3" t="n"/>
+      <c r="Z39" s="3" t="n"/>
+      <c r="AA39" s="3" t="n"/>
+      <c r="AB39" s="3" t="n"/>
+      <c r="AC39" s="4" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="B40" s="36" t="n"/>
-      <c r="AC40" s="37" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="AC40" s="7" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="B41" s="36" t="n"/>
-      <c r="AC41" s="37" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="AC41" s="7" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="B42" s="36" t="n"/>
-      <c r="AC42" s="37" t="n"/>
+      <c r="B42" s="5" t="n"/>
+      <c r="AC42" s="7" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="B43" s="36" t="n"/>
-      <c r="AC43" s="37" t="n"/>
+      <c r="B43" s="5" t="n"/>
+      <c r="AC43" s="7" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="B44" s="36" t="n"/>
-      <c r="AC44" s="37" t="n"/>
+      <c r="B44" s="5" t="n"/>
+      <c r="AC44" s="7" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="B45" s="36" t="n"/>
-      <c r="AC45" s="37" t="n"/>
+      <c r="B45" s="5" t="n"/>
+      <c r="AC45" s="7" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="B46" s="36" t="n"/>
-      <c r="AC46" s="37" t="n"/>
+      <c r="B46" s="5" t="n"/>
+      <c r="AC46" s="7" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1">
-      <c r="B47" s="38" t="n"/>
-      <c r="C47" s="32" t="n"/>
-      <c r="D47" s="32" t="n"/>
-      <c r="E47" s="32" t="n"/>
-      <c r="F47" s="32" t="n"/>
-      <c r="G47" s="32" t="n"/>
-      <c r="H47" s="32" t="n"/>
-      <c r="I47" s="32" t="n"/>
-      <c r="J47" s="32" t="n"/>
-      <c r="K47" s="32" t="n"/>
-      <c r="L47" s="32" t="n"/>
-      <c r="M47" s="32" t="n"/>
-      <c r="N47" s="32" t="n"/>
-      <c r="O47" s="32" t="n"/>
-      <c r="P47" s="32" t="n"/>
-      <c r="Q47" s="32" t="n"/>
-      <c r="R47" s="32" t="n"/>
-      <c r="S47" s="32" t="n"/>
-      <c r="T47" s="32" t="n"/>
-      <c r="U47" s="32" t="n"/>
-      <c r="V47" s="32" t="n"/>
-      <c r="W47" s="32" t="n"/>
-      <c r="X47" s="32" t="n"/>
-      <c r="Y47" s="32" t="n"/>
-      <c r="Z47" s="32" t="n"/>
-      <c r="AA47" s="32" t="n"/>
-      <c r="AB47" s="32" t="n"/>
-      <c r="AC47" s="39" t="n"/>
+      <c r="B47" s="8" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="9" t="n"/>
+      <c r="I47" s="9" t="n"/>
+      <c r="J47" s="9" t="n"/>
+      <c r="K47" s="9" t="n"/>
+      <c r="L47" s="9" t="n"/>
+      <c r="M47" s="9" t="n"/>
+      <c r="N47" s="9" t="n"/>
+      <c r="O47" s="9" t="n"/>
+      <c r="P47" s="9" t="n"/>
+      <c r="Q47" s="9" t="n"/>
+      <c r="R47" s="9" t="n"/>
+      <c r="S47" s="9" t="n"/>
+      <c r="T47" s="9" t="n"/>
+      <c r="U47" s="9" t="n"/>
+      <c r="V47" s="9" t="n"/>
+      <c r="W47" s="9" t="n"/>
+      <c r="X47" s="9" t="n"/>
+      <c r="Y47" s="9" t="n"/>
+      <c r="Z47" s="9" t="n"/>
+      <c r="AA47" s="9" t="n"/>
+      <c r="AB47" s="9" t="n"/>
+      <c r="AC47" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B22:AC23"/>
     <mergeCell ref="B2:AC3"/>
-    <mergeCell ref="B24:AC31"/>
-    <mergeCell ref="B33:AC34"/>
-    <mergeCell ref="B6:AC21"/>
-    <mergeCell ref="B35:AC47"/>
+    <mergeCell ref="B25:AC26"/>
+    <mergeCell ref="B37:AC38"/>
+    <mergeCell ref="B27:AC35"/>
+    <mergeCell ref="B6:AC24"/>
     <mergeCell ref="B4:AC5"/>
+    <mergeCell ref="B39:AC47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" scale="99"/>
@@ -2058,11 +2069,11 @@
   <dimension ref="B2:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="6" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>2-2.分析① 月齢別</t>
         </is>
@@ -2070,7 +2081,7 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="25" ht="15" customHeight="1">
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>2-2.分析② 学年別</t>
         </is>
@@ -2097,11 +2108,11 @@
   <dimension ref="B2:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="6" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>2-2.分析③ 登園月数</t>
         </is>
@@ -2109,7 +2120,7 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="25" ht="15" customHeight="1">
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>2-2.分析④ 登園年数別</t>
         </is>
@@ -2136,11 +2147,11 @@
   <dimension ref="B2:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="6" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>2-2.分析⑤ 月間</t>
         </is>
@@ -2148,7 +2159,7 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="25" ht="15" customHeight="1">
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>2-2.分析⑥ 月別</t>
         </is>
@@ -2175,11 +2186,11 @@
   <dimension ref="B2:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="6" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>2-2.分析 傾向考察</t>
         </is>
@@ -2187,346 +2198,354 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="4" ht="15" customHeight="1">
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>■ 考察</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="32" t="n"/>
-      <c r="C5" s="32" t="n"/>
-      <c r="D5" s="32" t="n"/>
-      <c r="E5" s="32" t="n"/>
-      <c r="F5" s="32" t="n"/>
-      <c r="G5" s="32" t="n"/>
-      <c r="H5" s="32" t="n"/>
-      <c r="I5" s="32" t="n"/>
-      <c r="J5" s="32" t="n"/>
-      <c r="K5" s="32" t="n"/>
-      <c r="L5" s="32" t="n"/>
-      <c r="M5" s="32" t="n"/>
-      <c r="N5" s="32" t="n"/>
-      <c r="O5" s="32" t="n"/>
-      <c r="P5" s="32" t="n"/>
-      <c r="Q5" s="32" t="n"/>
-      <c r="R5" s="32" t="n"/>
-      <c r="S5" s="32" t="n"/>
-      <c r="T5" s="32" t="n"/>
-      <c r="U5" s="32" t="n"/>
-      <c r="V5" s="32" t="n"/>
-      <c r="W5" s="32" t="n"/>
-      <c r="X5" s="32" t="n"/>
-      <c r="Y5" s="32" t="n"/>
-      <c r="Z5" s="32" t="n"/>
-      <c r="AA5" s="32" t="n"/>
-      <c r="AB5" s="32" t="n"/>
-      <c r="AC5" s="32" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="9" t="n"/>
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" s="9" t="n"/>
+      <c r="M5" s="9" t="n"/>
+      <c r="N5" s="9" t="n"/>
+      <c r="O5" s="9" t="n"/>
+      <c r="P5" s="9" t="n"/>
+      <c r="Q5" s="9" t="n"/>
+      <c r="R5" s="9" t="n"/>
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="9" t="n"/>
+      <c r="U5" s="9" t="n"/>
+      <c r="V5" s="9" t="n"/>
+      <c r="W5" s="9" t="n"/>
+      <c r="X5" s="9" t="n"/>
+      <c r="Y5" s="9" t="n"/>
+      <c r="Z5" s="9" t="n"/>
+      <c r="AA5" s="9" t="n"/>
+      <c r="AB5" s="9" t="n"/>
+      <c r="AC5" s="9" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="33" t="inlineStr">
-        <is>
-          <t>月齢別の平均欠席日数は約3.0～3.0日で推移しており、大きな差は認められなかった。
-学年別の平均欠席日数は約9.0～8.5日で推移しており、学年間で大きな差は認められなかった。
-登園月数別の平均欠席日数は約3.0～3.0日で推移しており、登園月数による大きな差は認められなかった。
-登園年数が短い時期の平均欠席日数は約48.5日であり、在園年数の増加とともに約3.0日まで減少した。全体で約45.5日の改善がみられ、園生活への適応や生活習慣の定着に伴い、欠席日数が減少する傾向が確認された。
-月別では1月の平均欠席日数が約22.0日と最も高く、季節性による影響が比較的強く現れていることが示唆された。
-月間平均欠席日数は約3.0～3.0日で推移しており、全体として大きな変動は認められなかった。</t>
-        </is>
-      </c>
-      <c r="C6" s="34" t="n"/>
-      <c r="D6" s="34" t="n"/>
-      <c r="E6" s="34" t="n"/>
-      <c r="F6" s="34" t="n"/>
-      <c r="G6" s="34" t="n"/>
-      <c r="H6" s="34" t="n"/>
-      <c r="I6" s="34" t="n"/>
-      <c r="J6" s="34" t="n"/>
-      <c r="K6" s="34" t="n"/>
-      <c r="L6" s="34" t="n"/>
-      <c r="M6" s="34" t="n"/>
-      <c r="N6" s="34" t="n"/>
-      <c r="O6" s="34" t="n"/>
-      <c r="P6" s="34" t="n"/>
-      <c r="Q6" s="34" t="n"/>
-      <c r="R6" s="34" t="n"/>
-      <c r="S6" s="34" t="n"/>
-      <c r="T6" s="34" t="n"/>
-      <c r="U6" s="34" t="n"/>
-      <c r="V6" s="34" t="n"/>
-      <c r="W6" s="34" t="n"/>
-      <c r="X6" s="34" t="n"/>
-      <c r="Y6" s="34" t="n"/>
-      <c r="Z6" s="34" t="n"/>
-      <c r="AA6" s="34" t="n"/>
-      <c r="AB6" s="34" t="n"/>
-      <c r="AC6" s="35" t="n"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>【子供001】
+月齢が上がるにつれて平均欠席日数は約3.0日から約5.0日へ増加した。
+学年が上がるにつれて平均欠席日数は約18.0日から約0.0日へ減少した。
+登園月数の経過に伴い平均欠席日数は約3.0日から約5.0日へ増加した。
+登園年数の経過に伴い平均欠席日数は約58.0日から約5.0日へ減少した。
+2月の平均欠席日数が約25.0日と最も高く、季節性の影響がみられた。
+月間推移では平均欠席日数が約3.0日から約5.0日へ増加した。
+【子供002】
+月齢が上がるにつれて平均欠席日数は約3.0日から約1.0日へ減少した。
+学年が上がるにつれて平均欠席日数は約0.0日から約17.0日へ増加した。
+登園月数の経過に伴い平均欠席日数は約3.0日から約1.0日へ減少した。
+登園年数の経過に伴い平均欠席日数は約39.0日から約1.0日へ減少した。
+1月の平均欠席日数が約22.0日と最も高く、季節性の影響がみられた。
+月間推移では平均欠席日数が約3.0日から約1.0日へ減少した。</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="n"/>
+      <c r="Q6" s="3" t="n"/>
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" s="3" t="n"/>
+      <c r="T6" s="3" t="n"/>
+      <c r="U6" s="3" t="n"/>
+      <c r="V6" s="3" t="n"/>
+      <c r="W6" s="3" t="n"/>
+      <c r="X6" s="3" t="n"/>
+      <c r="Y6" s="3" t="n"/>
+      <c r="Z6" s="3" t="n"/>
+      <c r="AA6" s="3" t="n"/>
+      <c r="AB6" s="3" t="n"/>
+      <c r="AC6" s="4" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="36" t="n"/>
-      <c r="AC7" s="37" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="AC7" s="7" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="36" t="n"/>
-      <c r="AC8" s="37" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="AC8" s="7" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="B9" s="36" t="n"/>
-      <c r="AC9" s="37" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="AC9" s="7" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="36" t="n"/>
-      <c r="AC10" s="37" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="AC10" s="7" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
-      <c r="B11" s="36" t="n"/>
-      <c r="AC11" s="37" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="AC11" s="7" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
-      <c r="B12" s="36" t="n"/>
-      <c r="AC12" s="37" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="AC12" s="7" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="B13" s="36" t="n"/>
-      <c r="AC13" s="37" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="AC13" s="7" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="36" t="n"/>
-      <c r="AC14" s="37" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="AC14" s="7" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="B15" s="36" t="n"/>
-      <c r="AC15" s="37" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="AC15" s="7" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="36" t="n"/>
-      <c r="AC16" s="37" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="AC16" s="7" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="36" t="n"/>
-      <c r="AC17" s="37" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="AC17" s="7" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="36" t="n"/>
-      <c r="AC18" s="37" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="AC18" s="7" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="B19" s="36" t="n"/>
-      <c r="AC19" s="37" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="AC19" s="7" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="B20" s="36" t="n"/>
-      <c r="AC20" s="37" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="AC20" s="7" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="B21" s="36" t="n"/>
-      <c r="AC21" s="37" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="AC21" s="7" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="36" t="n"/>
-      <c r="AC22" s="37" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="AC22" s="7" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="36" t="n"/>
-      <c r="AC23" s="37" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="AC23" s="7" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="B24" s="38" t="n"/>
-      <c r="C24" s="32" t="n"/>
-      <c r="D24" s="32" t="n"/>
-      <c r="E24" s="32" t="n"/>
-      <c r="F24" s="32" t="n"/>
-      <c r="G24" s="32" t="n"/>
-      <c r="H24" s="32" t="n"/>
-      <c r="I24" s="32" t="n"/>
-      <c r="J24" s="32" t="n"/>
-      <c r="K24" s="32" t="n"/>
-      <c r="L24" s="32" t="n"/>
-      <c r="M24" s="32" t="n"/>
-      <c r="N24" s="32" t="n"/>
-      <c r="O24" s="32" t="n"/>
-      <c r="P24" s="32" t="n"/>
-      <c r="Q24" s="32" t="n"/>
-      <c r="R24" s="32" t="n"/>
-      <c r="S24" s="32" t="n"/>
-      <c r="T24" s="32" t="n"/>
-      <c r="U24" s="32" t="n"/>
-      <c r="V24" s="32" t="n"/>
-      <c r="W24" s="32" t="n"/>
-      <c r="X24" s="32" t="n"/>
-      <c r="Y24" s="32" t="n"/>
-      <c r="Z24" s="32" t="n"/>
-      <c r="AA24" s="32" t="n"/>
-      <c r="AB24" s="32" t="n"/>
-      <c r="AC24" s="39" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="9" t="n"/>
+      <c r="I24" s="9" t="n"/>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
+      <c r="L24" s="9" t="n"/>
+      <c r="M24" s="9" t="n"/>
+      <c r="N24" s="9" t="n"/>
+      <c r="O24" s="9" t="n"/>
+      <c r="P24" s="9" t="n"/>
+      <c r="Q24" s="9" t="n"/>
+      <c r="R24" s="9" t="n"/>
+      <c r="S24" s="9" t="n"/>
+      <c r="T24" s="9" t="n"/>
+      <c r="U24" s="9" t="n"/>
+      <c r="V24" s="9" t="n"/>
+      <c r="W24" s="9" t="n"/>
+      <c r="X24" s="9" t="n"/>
+      <c r="Y24" s="9" t="n"/>
+      <c r="Z24" s="9" t="n"/>
+      <c r="AA24" s="9" t="n"/>
+      <c r="AB24" s="9" t="n"/>
+      <c r="AC24" s="10" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>■ 業務改善提案</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="B27" s="32" t="n"/>
-      <c r="C27" s="32" t="n"/>
-      <c r="D27" s="32" t="n"/>
-      <c r="E27" s="32" t="n"/>
-      <c r="F27" s="32" t="n"/>
-      <c r="G27" s="32" t="n"/>
-      <c r="H27" s="32" t="n"/>
-      <c r="I27" s="32" t="n"/>
-      <c r="J27" s="32" t="n"/>
-      <c r="K27" s="32" t="n"/>
-      <c r="L27" s="32" t="n"/>
-      <c r="M27" s="32" t="n"/>
-      <c r="N27" s="32" t="n"/>
-      <c r="O27" s="32" t="n"/>
-      <c r="P27" s="32" t="n"/>
-      <c r="Q27" s="32" t="n"/>
-      <c r="R27" s="32" t="n"/>
-      <c r="S27" s="32" t="n"/>
-      <c r="T27" s="32" t="n"/>
-      <c r="U27" s="32" t="n"/>
-      <c r="V27" s="32" t="n"/>
-      <c r="W27" s="32" t="n"/>
-      <c r="X27" s="32" t="n"/>
-      <c r="Y27" s="32" t="n"/>
-      <c r="Z27" s="32" t="n"/>
-      <c r="AA27" s="32" t="n"/>
-      <c r="AB27" s="32" t="n"/>
-      <c r="AC27" s="32" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="9" t="n"/>
+      <c r="I27" s="9" t="n"/>
+      <c r="J27" s="9" t="n"/>
+      <c r="K27" s="9" t="n"/>
+      <c r="L27" s="9" t="n"/>
+      <c r="M27" s="9" t="n"/>
+      <c r="N27" s="9" t="n"/>
+      <c r="O27" s="9" t="n"/>
+      <c r="P27" s="9" t="n"/>
+      <c r="Q27" s="9" t="n"/>
+      <c r="R27" s="9" t="n"/>
+      <c r="S27" s="9" t="n"/>
+      <c r="T27" s="9" t="n"/>
+      <c r="U27" s="9" t="n"/>
+      <c r="V27" s="9" t="n"/>
+      <c r="W27" s="9" t="n"/>
+      <c r="X27" s="9" t="n"/>
+      <c r="Y27" s="9" t="n"/>
+      <c r="Z27" s="9" t="n"/>
+      <c r="AA27" s="9" t="n"/>
+      <c r="AB27" s="9" t="n"/>
+      <c r="AC27" s="9" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="B28" s="33" t="inlineStr">
-        <is>
-          <t>過去データおよびAI予測結果を踏まえると、年齢や登園初期、季節要因によって欠席日数が増加する傾向が確認された。
-これらの時期には感染症対策や健康観察を強化するとともに、家庭との情報共有を継続することが重要である。
-・子供001：平均欠席日数は約3.2日と予測され、予測期間内では安定基準への到達が見込まれなかった。健康観察を継続するとともに、家庭との情報共有や個別支援を強化することが望ましい。
-・子供002：平均欠席日数は約2.0日と予測され、予測期間内では安定基準への到達が見込まれなかった。健康観察を継続するとともに、家庭との情報共有や個別支援を強化することが望ましい。</t>
-        </is>
-      </c>
-      <c r="C28" s="34" t="n"/>
-      <c r="D28" s="34" t="n"/>
-      <c r="E28" s="34" t="n"/>
-      <c r="F28" s="34" t="n"/>
-      <c r="G28" s="34" t="n"/>
-      <c r="H28" s="34" t="n"/>
-      <c r="I28" s="34" t="n"/>
-      <c r="J28" s="34" t="n"/>
-      <c r="K28" s="34" t="n"/>
-      <c r="L28" s="34" t="n"/>
-      <c r="M28" s="34" t="n"/>
-      <c r="N28" s="34" t="n"/>
-      <c r="O28" s="34" t="n"/>
-      <c r="P28" s="34" t="n"/>
-      <c r="Q28" s="34" t="n"/>
-      <c r="R28" s="34" t="n"/>
-      <c r="S28" s="34" t="n"/>
-      <c r="T28" s="34" t="n"/>
-      <c r="U28" s="34" t="n"/>
-      <c r="V28" s="34" t="n"/>
-      <c r="W28" s="34" t="n"/>
-      <c r="X28" s="34" t="n"/>
-      <c r="Y28" s="34" t="n"/>
-      <c r="Z28" s="34" t="n"/>
-      <c r="AA28" s="34" t="n"/>
-      <c r="AB28" s="34" t="n"/>
-      <c r="AC28" s="35" t="n"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>【子供001】
+平均欠席日数は約3.2日と予測された。予測期間内で安定化は見込まれないため、健康観察や個別支援を継続することが望ましい。
+【子供002】
+平均欠席日数は約2.0日と予測された。予測期間内で安定化は見込まれないため、健康観察や個別支援を継続することが望ましい。</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n"/>
+      <c r="D28" s="3" t="n"/>
+      <c r="E28" s="3" t="n"/>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="3" t="n"/>
+      <c r="K28" s="3" t="n"/>
+      <c r="L28" s="3" t="n"/>
+      <c r="M28" s="3" t="n"/>
+      <c r="N28" s="3" t="n"/>
+      <c r="O28" s="3" t="n"/>
+      <c r="P28" s="3" t="n"/>
+      <c r="Q28" s="3" t="n"/>
+      <c r="R28" s="3" t="n"/>
+      <c r="S28" s="3" t="n"/>
+      <c r="T28" s="3" t="n"/>
+      <c r="U28" s="3" t="n"/>
+      <c r="V28" s="3" t="n"/>
+      <c r="W28" s="3" t="n"/>
+      <c r="X28" s="3" t="n"/>
+      <c r="Y28" s="3" t="n"/>
+      <c r="Z28" s="3" t="n"/>
+      <c r="AA28" s="3" t="n"/>
+      <c r="AB28" s="3" t="n"/>
+      <c r="AC28" s="4" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="36" t="n"/>
-      <c r="AC29" s="37" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="AC29" s="7" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="B30" s="36" t="n"/>
-      <c r="AC30" s="37" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="AC30" s="7" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="B31" s="36" t="n"/>
-      <c r="AC31" s="37" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="AC31" s="7" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="B32" s="36" t="n"/>
-      <c r="AC32" s="37" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="AC32" s="7" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="B33" s="36" t="n"/>
-      <c r="AC33" s="37" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="AC33" s="7" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="B34" s="36" t="n"/>
-      <c r="AC34" s="37" t="n"/>
+      <c r="B34" s="5" t="n"/>
+      <c r="AC34" s="7" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="B35" s="36" t="n"/>
-      <c r="AC35" s="37" t="n"/>
+      <c r="B35" s="5" t="n"/>
+      <c r="AC35" s="7" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="B36" s="36" t="n"/>
-      <c r="AC36" s="37" t="n"/>
+      <c r="B36" s="5" t="n"/>
+      <c r="AC36" s="7" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="B37" s="36" t="n"/>
-      <c r="AC37" s="37" t="n"/>
+      <c r="B37" s="5" t="n"/>
+      <c r="AC37" s="7" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="B38" s="36" t="n"/>
-      <c r="AC38" s="37" t="n"/>
+      <c r="B38" s="5" t="n"/>
+      <c r="AC38" s="7" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="B39" s="36" t="n"/>
-      <c r="AC39" s="37" t="n"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="AC39" s="7" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="B40" s="36" t="n"/>
-      <c r="AC40" s="37" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="AC40" s="7" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="B41" s="36" t="n"/>
-      <c r="AC41" s="37" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="AC41" s="7" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="B42" s="36" t="n"/>
-      <c r="AC42" s="37" t="n"/>
+      <c r="B42" s="5" t="n"/>
+      <c r="AC42" s="7" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="B43" s="36" t="n"/>
-      <c r="AC43" s="37" t="n"/>
+      <c r="B43" s="5" t="n"/>
+      <c r="AC43" s="7" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="B44" s="36" t="n"/>
-      <c r="AC44" s="37" t="n"/>
+      <c r="B44" s="5" t="n"/>
+      <c r="AC44" s="7" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="B45" s="38" t="n"/>
-      <c r="C45" s="32" t="n"/>
-      <c r="D45" s="32" t="n"/>
-      <c r="E45" s="32" t="n"/>
-      <c r="F45" s="32" t="n"/>
-      <c r="G45" s="32" t="n"/>
-      <c r="H45" s="32" t="n"/>
-      <c r="I45" s="32" t="n"/>
-      <c r="J45" s="32" t="n"/>
-      <c r="K45" s="32" t="n"/>
-      <c r="L45" s="32" t="n"/>
-      <c r="M45" s="32" t="n"/>
-      <c r="N45" s="32" t="n"/>
-      <c r="O45" s="32" t="n"/>
-      <c r="P45" s="32" t="n"/>
-      <c r="Q45" s="32" t="n"/>
-      <c r="R45" s="32" t="n"/>
-      <c r="S45" s="32" t="n"/>
-      <c r="T45" s="32" t="n"/>
-      <c r="U45" s="32" t="n"/>
-      <c r="V45" s="32" t="n"/>
-      <c r="W45" s="32" t="n"/>
-      <c r="X45" s="32" t="n"/>
-      <c r="Y45" s="32" t="n"/>
-      <c r="Z45" s="32" t="n"/>
-      <c r="AA45" s="32" t="n"/>
-      <c r="AB45" s="32" t="n"/>
-      <c r="AC45" s="39" t="n"/>
+      <c r="B45" s="8" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+      <c r="I45" s="9" t="n"/>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="9" t="n"/>
+      <c r="L45" s="9" t="n"/>
+      <c r="M45" s="9" t="n"/>
+      <c r="N45" s="9" t="n"/>
+      <c r="O45" s="9" t="n"/>
+      <c r="P45" s="9" t="n"/>
+      <c r="Q45" s="9" t="n"/>
+      <c r="R45" s="9" t="n"/>
+      <c r="S45" s="9" t="n"/>
+      <c r="T45" s="9" t="n"/>
+      <c r="U45" s="9" t="n"/>
+      <c r="V45" s="9" t="n"/>
+      <c r="W45" s="9" t="n"/>
+      <c r="X45" s="9" t="n"/>
+      <c r="Y45" s="9" t="n"/>
+      <c r="Z45" s="9" t="n"/>
+      <c r="AA45" s="9" t="n"/>
+      <c r="AB45" s="9" t="n"/>
+      <c r="AC45" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2550,11 +2569,11 @@
   <dimension ref="B2:AC3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="6" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>2-2.分析⑦ 未来リスク</t>
         </is>

--- a/output/reports/サンプル/サンプル2.xlsx
+++ b/output/reports/サンプル/サンプル2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="108" windowWidth="9708" windowHeight="12816" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'表紙'!$A$1:$AE$47</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'1'!$A$1:$AE$47</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'2'!$A$1:$AE$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'2'!$A$1:$AE$54</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'3'!$A$1:$AE$47</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'4'!$A$1:$AE$47</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'5'!$A$1:$AE$47</definedName>
@@ -375,10 +375,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -965,7 +965,7 @@
   <dimension ref="C12:AB44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="11" ht="15" customHeight="1" thickBot="1"/>
@@ -1048,7 +1048,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="J44" s="11" t="inlineStr">
         <is>
-          <t>2026/07/07</t>
+          <t>2026/07/09</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
   <dimension ref="B2:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
@@ -1348,10 +1348,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:AC51"/>
+  <dimension ref="B2:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
@@ -1363,7 +1363,7 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="4" ht="15" customHeight="1">
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>■ 主な傾向</t>
         </is>
@@ -1585,7 +1585,7 @@
       <c r="AC34" s="39" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="B35" s="31" t="inlineStr">
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>■ 未来予測結果</t>
         </is>
@@ -1625,9 +1625,9 @@
       <c r="B37" s="33" t="inlineStr">
         <is>
           <t>【子供001】
-平均欠席日数は約3.2日と予測された。予測期間内に安定基準へ到達しないと予測された。
+平均欠席日数は約3.2日（予測範囲：約1.3～5.9日）と予測された。予測期間内に安定基準へ到達しないと予測された。
 【子供002】
-平均欠席日数は約2.0日と予測された。予測期間内に安定基準へ到達しないと予測された。</t>
+平均欠席日数は約2.0日（予測範囲：約0.8～3.6日）と予測された。予測期間内に安定基準へ到達しないと予測された。</t>
         </is>
       </c>
       <c r="C37" s="34" t="n"/>
@@ -1671,120 +1671,120 @@
       <c r="AC40" s="37" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="B41" s="38" t="n"/>
-      <c r="C41" s="32" t="n"/>
-      <c r="D41" s="32" t="n"/>
-      <c r="E41" s="32" t="n"/>
-      <c r="F41" s="32" t="n"/>
-      <c r="G41" s="32" t="n"/>
-      <c r="H41" s="32" t="n"/>
-      <c r="I41" s="32" t="n"/>
-      <c r="J41" s="32" t="n"/>
-      <c r="K41" s="32" t="n"/>
-      <c r="L41" s="32" t="n"/>
-      <c r="M41" s="32" t="n"/>
-      <c r="N41" s="32" t="n"/>
-      <c r="O41" s="32" t="n"/>
-      <c r="P41" s="32" t="n"/>
-      <c r="Q41" s="32" t="n"/>
-      <c r="R41" s="32" t="n"/>
-      <c r="S41" s="32" t="n"/>
-      <c r="T41" s="32" t="n"/>
-      <c r="U41" s="32" t="n"/>
-      <c r="V41" s="32" t="n"/>
-      <c r="W41" s="32" t="n"/>
-      <c r="X41" s="32" t="n"/>
-      <c r="Y41" s="32" t="n"/>
-      <c r="Z41" s="32" t="n"/>
-      <c r="AA41" s="32" t="n"/>
-      <c r="AB41" s="32" t="n"/>
-      <c r="AC41" s="39" t="n"/>
+      <c r="B41" s="36" t="n"/>
+      <c r="AC41" s="37" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="B42" s="31" t="inlineStr">
+      <c r="B42" s="36" t="n"/>
+      <c r="AC42" s="37" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="B43" s="36" t="n"/>
+      <c r="AC43" s="37" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="B44" s="38" t="n"/>
+      <c r="C44" s="32" t="n"/>
+      <c r="D44" s="32" t="n"/>
+      <c r="E44" s="32" t="n"/>
+      <c r="F44" s="32" t="n"/>
+      <c r="G44" s="32" t="n"/>
+      <c r="H44" s="32" t="n"/>
+      <c r="I44" s="32" t="n"/>
+      <c r="J44" s="32" t="n"/>
+      <c r="K44" s="32" t="n"/>
+      <c r="L44" s="32" t="n"/>
+      <c r="M44" s="32" t="n"/>
+      <c r="N44" s="32" t="n"/>
+      <c r="O44" s="32" t="n"/>
+      <c r="P44" s="32" t="n"/>
+      <c r="Q44" s="32" t="n"/>
+      <c r="R44" s="32" t="n"/>
+      <c r="S44" s="32" t="n"/>
+      <c r="T44" s="32" t="n"/>
+      <c r="U44" s="32" t="n"/>
+      <c r="V44" s="32" t="n"/>
+      <c r="W44" s="32" t="n"/>
+      <c r="X44" s="32" t="n"/>
+      <c r="Y44" s="32" t="n"/>
+      <c r="Z44" s="32" t="n"/>
+      <c r="AA44" s="32" t="n"/>
+      <c r="AB44" s="32" t="n"/>
+      <c r="AC44" s="39" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="B45" s="30" t="inlineStr">
         <is>
           <t>■ 業務への示唆</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="B43" s="32" t="n"/>
-      <c r="C43" s="32" t="n"/>
-      <c r="D43" s="32" t="n"/>
-      <c r="E43" s="32" t="n"/>
-      <c r="F43" s="32" t="n"/>
-      <c r="G43" s="32" t="n"/>
-      <c r="H43" s="32" t="n"/>
-      <c r="I43" s="32" t="n"/>
-      <c r="J43" s="32" t="n"/>
-      <c r="K43" s="32" t="n"/>
-      <c r="L43" s="32" t="n"/>
-      <c r="M43" s="32" t="n"/>
-      <c r="N43" s="32" t="n"/>
-      <c r="O43" s="32" t="n"/>
-      <c r="P43" s="32" t="n"/>
-      <c r="Q43" s="32" t="n"/>
-      <c r="R43" s="32" t="n"/>
-      <c r="S43" s="32" t="n"/>
-      <c r="T43" s="32" t="n"/>
-      <c r="U43" s="32" t="n"/>
-      <c r="V43" s="32" t="n"/>
-      <c r="W43" s="32" t="n"/>
-      <c r="X43" s="32" t="n"/>
-      <c r="Y43" s="32" t="n"/>
-      <c r="Z43" s="32" t="n"/>
-      <c r="AA43" s="32" t="n"/>
-      <c r="AB43" s="32" t="n"/>
-      <c r="AC43" s="32" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="B44" s="33" t="inlineStr">
+    <row r="46" ht="15" customHeight="1">
+      <c r="B46" s="32" t="n"/>
+      <c r="C46" s="32" t="n"/>
+      <c r="D46" s="32" t="n"/>
+      <c r="E46" s="32" t="n"/>
+      <c r="F46" s="32" t="n"/>
+      <c r="G46" s="32" t="n"/>
+      <c r="H46" s="32" t="n"/>
+      <c r="I46" s="32" t="n"/>
+      <c r="J46" s="32" t="n"/>
+      <c r="K46" s="32" t="n"/>
+      <c r="L46" s="32" t="n"/>
+      <c r="M46" s="32" t="n"/>
+      <c r="N46" s="32" t="n"/>
+      <c r="O46" s="32" t="n"/>
+      <c r="P46" s="32" t="n"/>
+      <c r="Q46" s="32" t="n"/>
+      <c r="R46" s="32" t="n"/>
+      <c r="S46" s="32" t="n"/>
+      <c r="T46" s="32" t="n"/>
+      <c r="U46" s="32" t="n"/>
+      <c r="V46" s="32" t="n"/>
+      <c r="W46" s="32" t="n"/>
+      <c r="X46" s="32" t="n"/>
+      <c r="Y46" s="32" t="n"/>
+      <c r="Z46" s="32" t="n"/>
+      <c r="AA46" s="32" t="n"/>
+      <c r="AB46" s="32" t="n"/>
+      <c r="AC46" s="32" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="B47" s="33" t="inlineStr">
         <is>
           <t>【子供001】
-平均欠席日数は約3.2日と予測された。予測期間内で安定化は見込まれないため、健康観察や個別支援を継続することが望ましい。
+平均欠席日数は約3.2日と予測された。予測期間内で安定化は見込まれないため、継続的な欠席傾向の分析や、状況変化に応じた対応検討に活用することが望ましい。
 【子供002】
-平均欠席日数は約2.0日と予測された。予測期間内で安定化は見込まれないため、健康観察や個別支援を継続することが望ましい。</t>
-        </is>
-      </c>
-      <c r="C44" s="34" t="n"/>
-      <c r="D44" s="34" t="n"/>
-      <c r="E44" s="34" t="n"/>
-      <c r="F44" s="34" t="n"/>
-      <c r="G44" s="34" t="n"/>
-      <c r="H44" s="34" t="n"/>
-      <c r="I44" s="34" t="n"/>
-      <c r="J44" s="34" t="n"/>
-      <c r="K44" s="34" t="n"/>
-      <c r="L44" s="34" t="n"/>
-      <c r="M44" s="34" t="n"/>
-      <c r="N44" s="34" t="n"/>
-      <c r="O44" s="34" t="n"/>
-      <c r="P44" s="34" t="n"/>
-      <c r="Q44" s="34" t="n"/>
-      <c r="R44" s="34" t="n"/>
-      <c r="S44" s="34" t="n"/>
-      <c r="T44" s="34" t="n"/>
-      <c r="U44" s="34" t="n"/>
-      <c r="V44" s="34" t="n"/>
-      <c r="W44" s="34" t="n"/>
-      <c r="X44" s="34" t="n"/>
-      <c r="Y44" s="34" t="n"/>
-      <c r="Z44" s="34" t="n"/>
-      <c r="AA44" s="34" t="n"/>
-      <c r="AB44" s="34" t="n"/>
-      <c r="AC44" s="35" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="B45" s="36" t="n"/>
-      <c r="AC45" s="37" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="B46" s="36" t="n"/>
-      <c r="AC46" s="37" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="B47" s="36" t="n"/>
-      <c r="AC47" s="37" t="n"/>
+平均欠席日数は約2.0日と予測された。予測期間内で安定化は見込まれないため、継続的な欠席傾向の分析や、状況変化に応じた対応検討に活用することが望ましい。</t>
+        </is>
+      </c>
+      <c r="C47" s="34" t="n"/>
+      <c r="D47" s="34" t="n"/>
+      <c r="E47" s="34" t="n"/>
+      <c r="F47" s="34" t="n"/>
+      <c r="G47" s="34" t="n"/>
+      <c r="H47" s="34" t="n"/>
+      <c r="I47" s="34" t="n"/>
+      <c r="J47" s="34" t="n"/>
+      <c r="K47" s="34" t="n"/>
+      <c r="L47" s="34" t="n"/>
+      <c r="M47" s="34" t="n"/>
+      <c r="N47" s="34" t="n"/>
+      <c r="O47" s="34" t="n"/>
+      <c r="P47" s="34" t="n"/>
+      <c r="Q47" s="34" t="n"/>
+      <c r="R47" s="34" t="n"/>
+      <c r="S47" s="34" t="n"/>
+      <c r="T47" s="34" t="n"/>
+      <c r="U47" s="34" t="n"/>
+      <c r="V47" s="34" t="n"/>
+      <c r="W47" s="34" t="n"/>
+      <c r="X47" s="34" t="n"/>
+      <c r="Y47" s="34" t="n"/>
+      <c r="Z47" s="34" t="n"/>
+      <c r="AA47" s="34" t="n"/>
+      <c r="AB47" s="34" t="n"/>
+      <c r="AC47" s="35" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="B48" s="36" t="n"/>
@@ -1799,47 +1799,59 @@
       <c r="AC50" s="37" t="n"/>
     </row>
     <row r="51" ht="15" customHeight="1">
-      <c r="B51" s="38" t="n"/>
-      <c r="C51" s="32" t="n"/>
-      <c r="D51" s="32" t="n"/>
-      <c r="E51" s="32" t="n"/>
-      <c r="F51" s="32" t="n"/>
-      <c r="G51" s="32" t="n"/>
-      <c r="H51" s="32" t="n"/>
-      <c r="I51" s="32" t="n"/>
-      <c r="J51" s="32" t="n"/>
-      <c r="K51" s="32" t="n"/>
-      <c r="L51" s="32" t="n"/>
-      <c r="M51" s="32" t="n"/>
-      <c r="N51" s="32" t="n"/>
-      <c r="O51" s="32" t="n"/>
-      <c r="P51" s="32" t="n"/>
-      <c r="Q51" s="32" t="n"/>
-      <c r="R51" s="32" t="n"/>
-      <c r="S51" s="32" t="n"/>
-      <c r="T51" s="32" t="n"/>
-      <c r="U51" s="32" t="n"/>
-      <c r="V51" s="32" t="n"/>
-      <c r="W51" s="32" t="n"/>
-      <c r="X51" s="32" t="n"/>
-      <c r="Y51" s="32" t="n"/>
-      <c r="Z51" s="32" t="n"/>
-      <c r="AA51" s="32" t="n"/>
-      <c r="AB51" s="32" t="n"/>
-      <c r="AC51" s="39" t="n"/>
+      <c r="B51" s="36" t="n"/>
+      <c r="AC51" s="37" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="B52" s="36" t="n"/>
+      <c r="AC52" s="37" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="B53" s="36" t="n"/>
+      <c r="AC53" s="37" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="B54" s="38" t="n"/>
+      <c r="C54" s="32" t="n"/>
+      <c r="D54" s="32" t="n"/>
+      <c r="E54" s="32" t="n"/>
+      <c r="F54" s="32" t="n"/>
+      <c r="G54" s="32" t="n"/>
+      <c r="H54" s="32" t="n"/>
+      <c r="I54" s="32" t="n"/>
+      <c r="J54" s="32" t="n"/>
+      <c r="K54" s="32" t="n"/>
+      <c r="L54" s="32" t="n"/>
+      <c r="M54" s="32" t="n"/>
+      <c r="N54" s="32" t="n"/>
+      <c r="O54" s="32" t="n"/>
+      <c r="P54" s="32" t="n"/>
+      <c r="Q54" s="32" t="n"/>
+      <c r="R54" s="32" t="n"/>
+      <c r="S54" s="32" t="n"/>
+      <c r="T54" s="32" t="n"/>
+      <c r="U54" s="32" t="n"/>
+      <c r="V54" s="32" t="n"/>
+      <c r="W54" s="32" t="n"/>
+      <c r="X54" s="32" t="n"/>
+      <c r="Y54" s="32" t="n"/>
+      <c r="Z54" s="32" t="n"/>
+      <c r="AA54" s="32" t="n"/>
+      <c r="AB54" s="32" t="n"/>
+      <c r="AC54" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="B2:AC3"/>
-    <mergeCell ref="B37:AC41"/>
+    <mergeCell ref="B47:AC54"/>
     <mergeCell ref="B35:AC36"/>
-    <mergeCell ref="B42:AC43"/>
+    <mergeCell ref="B37:AC44"/>
+    <mergeCell ref="B45:AC46"/>
     <mergeCell ref="B6:AC34"/>
     <mergeCell ref="B4:AC5"/>
-    <mergeCell ref="B44:AC51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="93"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="88"/>
 </worksheet>
 </file>
 
@@ -1852,7 +1864,7 @@
   <dimension ref="B2:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
@@ -1891,7 +1903,7 @@
   <dimension ref="B2:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
@@ -1930,7 +1942,7 @@
   <dimension ref="B2:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
@@ -1969,7 +1981,7 @@
   <dimension ref="B2:AC3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
@@ -1999,7 +2011,7 @@
   <dimension ref="B2:AC46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
@@ -2011,7 +2023,7 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="4" ht="15" customHeight="1">
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>■ 考察</t>
         </is>
@@ -2237,7 +2249,7 @@
       <c r="AC35" s="39" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="B37" s="31" t="inlineStr">
+      <c r="B37" s="30" t="inlineStr">
         <is>
           <t>■ 業務改善提案</t>
         </is>
@@ -2277,9 +2289,9 @@
       <c r="B39" s="33" t="inlineStr">
         <is>
           <t>【子供001】
-平均欠席日数は約3.2日と予測された。予測期間内で安定化は見込まれないため、健康観察や個別支援を継続することが望ましい。
+平均欠席日数は約3.2日と予測された。予測期間内で安定化は見込まれないため、継続的な欠席傾向の分析や、状況変化に応じた対応検討に活用することが望ましい。
 【子供002】
-平均欠席日数は約2.0日と予測された。予測期間内で安定化は見込まれないため、健康観察や個別支援を継続することが望ましい。</t>
+平均欠席日数は約2.0日と予測された。予測期間内で安定化は見込まれないため、継続的な欠席傾向の分析や、状況変化に応じた対応検討に活用することが望ましい。</t>
         </is>
       </c>
       <c r="C39" s="34" t="n"/>
@@ -2386,7 +2398,7 @@
   <dimension ref="B2:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">

--- a/output/reports/サンプル/サンプル2.xlsx
+++ b/output/reports/サンプル/サンプル2.xlsx
@@ -2412,7 +2412,8 @@
     <row r="4" ht="15" customHeight="1">
       <c r="B4" s="33" t="inlineStr">
         <is>
-          <t>AIによる予測では、対象児童2名の平均欠席日数は約2.6日と推定された。予測期間内に安定化が見込まれる児童はおらず、継続的な欠席傾向の確認と、家庭と保育園・学校との連携が重要と考えられる。</t>
+          <t>AIによる予測では、対象児童2名の平均欠席日数は約2.6日と推定された。予測期間内に安定化が見込まれる児童はおらず、継続的な欠席傾向の確認と、家庭と保育園・学校との連携が重要と考えられる。
+また、学習データに対する予測精度（平均絶対誤差：MAE）は子供001：0.29日、子供002：0.20日であり、学習データの傾向を概ね再現できていることを確認した。</t>
         </is>
       </c>
       <c r="C4" s="34" t="n"/>

--- a/output/reports/サンプル/サンプル2.xlsx
+++ b/output/reports/サンプル/サンプル2.xlsx
@@ -2413,7 +2413,7 @@
       <c r="B4" s="33" t="inlineStr">
         <is>
           <t>AIによる予測では、対象児童2名の平均欠席日数は約2.6日と推定された。予測期間内に安定化が見込まれる児童はおらず、継続的な欠席傾向の確認と、家庭と保育園・学校との連携が重要と考えられる。
-また、学習データに対する予測精度（平均絶対誤差：MAE）は子供001：0.29日、子供002：0.20日であり、学習データの傾向を概ね再現できていることを確認した。</t>
+また、モデルの学習状況を確認するため、学習データに対する予測誤差（平均絶対誤差：MAE）を算出した。その結果、MAEは子供001：0.29日、子供002：0.20日であった。</t>
         </is>
       </c>
       <c r="C4" s="34" t="n"/>
